--- a/Some Rocket Maker Weird Thing.xlsx
+++ b/Some Rocket Maker Weird Thing.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c1132a9a06cee12/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c1132a9a06cee12/Documents/SomRMWT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2413" documentId="8_{085A2D8C-39A3-49E4-8CEE-214FC540B867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1807E17A-87A4-43BA-BE6F-93B22162C3CE}"/>
+  <xr:revisionPtr revIDLastSave="3024" documentId="8_{085A2D8C-39A3-49E4-8CEE-214FC540B867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4540CE17-BD85-465E-AC4C-A9B3E5366989}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{255BFBE9-9FC6-44F8-AB9D-453C5CE9D40B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{255BFBE9-9FC6-44F8-AB9D-453C5CE9D40B}"/>
   </bookViews>
   <sheets>
     <sheet name="Le Intro" sheetId="2" r:id="rId1"/>
     <sheet name="Data Input" sheetId="5" r:id="rId2"/>
     <sheet name="Initial Sizing" sheetId="1" r:id="rId3"/>
-    <sheet name="Log" sheetId="3" r:id="rId4"/>
+    <sheet name="Geometry" sheetId="7" r:id="rId4"/>
+    <sheet name="Weight Analysis - Initial" sheetId="6" r:id="rId5"/>
+    <sheet name="Log" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="20000" iterateDelta="1E-4" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -305,6 +307,40 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Muhammad Naufal Afif</author>
+  </authors>
+  <commentList>
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{CB5F8879-9A8E-4DE4-A71E-B990AF1125CF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Muhammad Naufal Afif:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Fill as many as stages in rocket and none else</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="2">
@@ -320,7 +356,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -331,7 +367,14 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -341,12 +384,15 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="3">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -387,7 +433,7 @@
     </pythonScript>
     <pythonScript>
       <code xml:space="preserve">from statistics import geometric_mean
-subset = data_input_df.loc["Assumed ideal single stage delta-v requirement", "Primary Mission":"Mission #10"]
+subset = data_input_df.loc["Assumed ideal single-stage delta-v requirement", "Primary Mission":"Mission #10"]
 try: 
     float_values = subset[subset.apply(lambda x: isinstance(x, float))]
     wadidaw = geometric_mean(float_values)
@@ -433,6 +479,11 @@
 except: 
     wadidaw = "¯\_(ツ)_/¯"
 wadidaw</code>
+    </pythonScript>
+    <pythonScript>
+      <code>from pathlib import Path as p_ingfo
+with open(f"{p_ingfo.cwd()}//Python Dependencies//init_sizing.py") as bruh:
+     exec(bruh.read())</code>
     </pythonScript>
     <pythonScript>
       <code xml:space="preserve">init_sizing_df = xl(%P2%, headers=True)
@@ -506,7 +557,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="289">
   <si>
     <t>Stage</t>
   </si>
@@ -556,9 +607,6 @@
     <t>Specific impulse</t>
   </si>
   <si>
-    <t>Delta-v</t>
-  </si>
-  <si>
     <t>Wet mass</t>
   </si>
   <si>
@@ -632,9 +680,6 @@
   </si>
   <si>
     <t>HOW TO OTHER TABLE</t>
-  </si>
-  <si>
-    <t>DO NOT TOUCH THE FIRST TWO COLUMNS!!! Insert fuel type in the fuel columns and subsequently its specific impulse in the respective columns. When one isn't available, SLIsp = 0.667*VacIsp and or VacIsp = 1.5*SLIsp</t>
   </si>
   <si>
     <t>Stage dry mass</t>
@@ -721,6 +766,797 @@
     </r>
   </si>
   <si>
+    <t>1. Added to-do list in Intro page
+2. Revised wording in Intro page</t>
+  </si>
+  <si>
+    <t>12/01/2025,15:01 UTC+7</t>
+  </si>
+  <si>
+    <t>13/01/2025, 05:18 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Added expected features</t>
+  </si>
+  <si>
+    <t>APCP</t>
+  </si>
+  <si>
+    <t>HTPB/Paraffin</t>
+  </si>
+  <si>
+    <t>LOX/HTPB</t>
+  </si>
+  <si>
+    <t>N2O4/MMH</t>
+  </si>
+  <si>
+    <t>N2O4/UDMH×N2H4
+(Aerozine 50)</t>
+  </si>
+  <si>
+    <t>N2O4/UDMH</t>
+  </si>
+  <si>
+    <t>Black powder</t>
+  </si>
+  <si>
+    <t>1. Uploaded file to Github for further collaboration</t>
+  </si>
+  <si>
+    <t>13/01/2025, 11:40 UTC+7</t>
+  </si>
+  <si>
+    <t>13/01/2025, 11:41 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Revised Github readme, therefore intro spreadsheet</t>
+  </si>
+  <si>
+    <t>CO-AUTHORS! PLEASE FILL IN LOG AFTER EDITING! UNLESS MAKING A NEW VERSION, UNLISTED CHANGES ARE NOT RECOGNISED AND WILL BE RECTIFIED!!!</t>
+  </si>
+  <si>
+    <t>[REP]</t>
+  </si>
+  <si>
+    <t>[TIO]</t>
+  </si>
+  <si>
+    <t>Ir. Toto Indriyanto, M.Sc., Ph.D.</t>
+  </si>
+  <si>
+    <t>Lecturer
+Aerospace Engineering Study Program, Faculty of Mechanic and Aerospace Engineering
+Institut Teknologi Bandung</t>
+  </si>
+  <si>
+    <t>Dr. Eng. Ridanto Eko Poetro, S.T, M.Sc.</t>
+  </si>
+  <si>
+    <t>13/01/2025, 11:51 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Some formatting changes to intro spreadsheet and or Github readme</t>
+  </si>
+  <si>
+    <t>Rocket Name</t>
+  </si>
+  <si>
+    <t>Expected Stages</t>
+  </si>
+  <si>
+    <t>Secondary Mission</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What kind of mission? </t>
+  </si>
+  <si>
+    <t>Primary Mission</t>
+  </si>
+  <si>
+    <t>Tertiary Mission</t>
+  </si>
+  <si>
+    <t>Mission #4</t>
+  </si>
+  <si>
+    <t>Mission #5</t>
+  </si>
+  <si>
+    <t>Mission #6</t>
+  </si>
+  <si>
+    <t>Mission #7</t>
+  </si>
+  <si>
+    <t>Mission #8</t>
+  </si>
+  <si>
+    <t>Mission #9</t>
+  </si>
+  <si>
+    <t>Mission #10</t>
+  </si>
+  <si>
+    <t>Expected Rocket Diameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What kind of orbit? </t>
+  </si>
+  <si>
+    <t>Expected semi-major axis</t>
+  </si>
+  <si>
+    <t>Easy enough. Just insert your data in the yellow-tinted cells, also the orange one if you're feeling frisky since those are optional. You can add more missions if you like. All other sheets refer to data inputed here</t>
+  </si>
+  <si>
+    <t>Expected gimbal angle</t>
+  </si>
+  <si>
+    <t>Expected mission orbit inclination</t>
+  </si>
+  <si>
+    <t>Expected Rocket Size (NASA)</t>
+  </si>
+  <si>
+    <t>Smoli (0 - 2000 kg)</t>
+  </si>
+  <si>
+    <t>Imouto (2000 - 20000 kg)</t>
+  </si>
+  <si>
+    <t>Beeg (20000 - 50000 lkg)</t>
+  </si>
+  <si>
+    <t>CHONKER (&gt; 50000 kg)</t>
+  </si>
+  <si>
+    <t>MEO</t>
+  </si>
+  <si>
+    <t>Interplanetary (to Sun)</t>
+  </si>
+  <si>
+    <t>Expected primary launch site latitude</t>
+  </si>
+  <si>
+    <t>Circular</t>
+  </si>
+  <si>
+    <t>Eliptical</t>
+  </si>
+  <si>
+    <t>Interplanetary (away from Sun)</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>Expected secondary launch site latitude</t>
+  </si>
+  <si>
+    <t>Total delta-v needed</t>
+  </si>
+  <si>
+    <t>(Boolean)</t>
+  </si>
+  <si>
+    <t>DO NOT EDIT THIS TABLE!!!</t>
+  </si>
+  <si>
+    <t>Expected Rocket Statistics</t>
+  </si>
+  <si>
+    <t>Average payload size</t>
+  </si>
+  <si>
+    <t>Average launch site inclination</t>
+  </si>
+  <si>
+    <t>Average total delta-v requirement</t>
+  </si>
+  <si>
+    <t>degrees</t>
+  </si>
+  <si>
+    <t>m.s^-1</t>
+  </si>
+  <si>
+    <t>ROwOcket</t>
+  </si>
+  <si>
+    <t>PRELIMINARY ROCKET STATS</t>
+  </si>
+  <si>
+    <t>13/01/2025, 19:21 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Data input</t>
+  </si>
+  <si>
+    <t>HOW TO TABLES</t>
+  </si>
+  <si>
+    <t>Ctrl+; and then Ctrl+Shift+; on the date and time cell before inserting your local time zone. Pick your abbreviation (that can be set on the orange table). State in a numbered list concisely what you've done. Copy your Github commits here if you came from there</t>
+  </si>
+  <si>
+    <t>1. Initial sizing sheet now interconnected with data input data
+2. Additional details on how to input logs
+3. Some more statistics on initial sizing</t>
+  </si>
+  <si>
+    <t>Single-stage delta-v for mission</t>
+  </si>
+  <si>
+    <t>LEO (ISS mission mostly)</t>
+  </si>
+  <si>
+    <t>Insert numbers in yellow-tinted cells. Boosters not supported yet, nor coasting</t>
+  </si>
+  <si>
+    <t>Average single-stage ideal delta-v</t>
+  </si>
+  <si>
+    <t>Translunar (assuming LEO parking orbit)</t>
+  </si>
+  <si>
+    <t>Trans-Mars (assuming LEO parking orbit)</t>
+  </si>
+  <si>
+    <t>NOR THIS ONE!!!</t>
+  </si>
+  <si>
+    <t>V: Orbit? | -&gt; Orbit type?</t>
+  </si>
+  <si>
+    <t>14/01/2025, 14:13 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Delta-v calculation in input sheet
+2. Started work on the orbital calculation for input (single-stage to desired orbit)</t>
+  </si>
+  <si>
+    <t>[JHS]</t>
+  </si>
+  <si>
+    <t>Parabolic</t>
+  </si>
+  <si>
+    <t>Expected (periapsis) radius</t>
+  </si>
+  <si>
+    <t>GEO/GTO</t>
+  </si>
+  <si>
+    <t>Hyperbolic (assuming a 1 km/s speed)</t>
+  </si>
+  <si>
+    <t>Desired Rocket Payload Ratio (0 -1)</t>
+  </si>
+  <si>
+    <t>Desired propellant mass fraction (0 - 1)</t>
+  </si>
+  <si>
+    <t>Desired dry mass ratio (0 - 1)</t>
+  </si>
+  <si>
+    <t>Liftoff weight</t>
+  </si>
+  <si>
+    <t>14/01/2025, 21:18 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Finally made data input work
+2. Proper initial sizing, about damn time</t>
+  </si>
+  <si>
+    <t>15/01/2025, 10:59 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Improved data input</t>
+  </si>
+  <si>
+    <t>16/01/2025, 08:51 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Improved initial sizing, now with Python!
+2. Put initial sizing data as pandas dataframe</t>
+  </si>
+  <si>
+    <t>Average orbit inclination</t>
+  </si>
+  <si>
+    <t>16/01/2025, 13:08 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Improved needed delta-v budget calculations</t>
+  </si>
+  <si>
+    <t>Benedict Julian Zefanya Batubara</t>
+  </si>
+  <si>
+    <t>[BJB]</t>
+  </si>
+  <si>
+    <t>16/01/2025, 16:18 UTC+7</t>
+  </si>
+  <si>
+    <t>Maximum total delta-v requirement</t>
+  </si>
+  <si>
+    <t>Fulfils average delta-v?</t>
+  </si>
+  <si>
+    <t>Fulfils max delta-v?</t>
+  </si>
+  <si>
+    <t>^ DO NOT EVER TOUCH THIS CELL!!!</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">References: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[OwO]</t>
+    </r>
+  </si>
+  <si>
+    <t>17/01/2025, 16:50 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Improved expected rocket statistics in data input: Now With Python!
+2. Improved log tracking
+3. Improved initial sizing</t>
+  </si>
+  <si>
+    <t>DO NOT EVER TOUCH THIS CELL!!! -&gt;</t>
+  </si>
+  <si>
+    <t>Optimise rocket?</t>
+  </si>
+  <si>
+    <t>Optimised delta-v budget</t>
+  </si>
+  <si>
+    <t>Calculated delta-v budget</t>
+  </si>
+  <si>
+    <t>22/01/2025, 16:30 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Revised Python code for data sizing
+2. Switched Python-enabled cell from being Python objects to become Excel values</t>
+  </si>
+  <si>
+    <t>1. "Goal seek" optimisation for rocket initial sizing</t>
+  </si>
+  <si>
+    <t>Graduate
+Aerospace Engineering Study Program, Faculty of Mechanic and Aerospace Engineering
+Institut Teknologi Bandung</t>
+  </si>
+  <si>
+    <t>20/08/2025, 14:20 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Revised lead contributor's position</t>
+  </si>
+  <si>
+    <t>Muhammad Naufal Afif, S.T.</t>
+  </si>
+  <si>
+    <t>[DAS]</t>
+  </si>
+  <si>
+    <t>David Soegijanto, S.T.</t>
+  </si>
+  <si>
+    <t>Graduate Student
+Aerospace Engineering Study Program, Faculty of Mechanic and Aerospace Engineering
+Institut Teknologi Bandung</t>
+  </si>
+  <si>
+    <t>21/08/2025, 21:46 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Added new contributor
+2. Update README.md in GitHub
+3. Updated SomRMWT in GitHub</t>
+  </si>
+  <si>
+    <t>1. Uploaded revision to GitHub
+     a.Officially added co-authors
+     b. Refined initial sizing algorithm</t>
+  </si>
+  <si>
+    <t>[BGD]</t>
+  </si>
+  <si>
+    <t>Graduate
+Computer Engineering Study Program, Faculty of Engineering
+Bina Nusantara University</t>
+  </si>
+  <si>
+    <t>Bagaskara Adhiguna, S.T.</t>
+  </si>
+  <si>
+    <t>Insert numbers in yellow-tinted cells, optionally in orange-tinted one.</t>
+  </si>
+  <si>
+    <t>Propellant mass fraction</t>
+  </si>
+  <si>
+    <t>Dry mass ratio</t>
+  </si>
+  <si>
+    <t>Max. possble delta-V, initial sizing (m*s^-1)</t>
+  </si>
+  <si>
+    <t>GLOW, initial sizing (kg)</t>
+  </si>
+  <si>
+    <t>Empty weight, initial sizing (kg)</t>
+  </si>
+  <si>
+    <t>Things inputted</t>
+  </si>
+  <si>
+    <t>Input value</t>
+  </si>
+  <si>
+    <t>Desired thrust-to-weight ratio</t>
+  </si>
+  <si>
+    <t>General subdvision</t>
+  </si>
+  <si>
+    <t>Specific subdivision</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Fuel type</t>
+  </si>
+  <si>
+    <t>Proportion, fuel</t>
+  </si>
+  <si>
+    <t>Proportion, oxidiser</t>
+  </si>
+  <si>
+    <t>N2O4/UDMH×N2H4 (Aerozine 50)</t>
+  </si>
+  <si>
+    <t>DON'T TOUCH THIS TABLE AAAAAAAAAAAAAAAAAAA--</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Propellant</t>
+  </si>
+  <si>
+    <t>Oxidiser</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Tanks</t>
+  </si>
+  <si>
+    <t>"Skeleton"</t>
+  </si>
+  <si>
+    <t>27/08/2025, 00:08 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Added contributor and revised position
+2. Cosmetic improvements</t>
+  </si>
+  <si>
+    <t>1. Fuel-oxidiser ratio table
+2. Weight Analysis - Initial
+3. Python coding as separate .py files for initial sizing and weight analysis</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>What Even Is This?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+SomRMWT is a rocket designer built using Excel and coded partially in Python, designed for hobby rocketry, academic purposes as teaching tool, or conceptual rocket designs. Started when Muhammad Naufal Afif was bored on his sixth year studying aerospace engineering, it provides "good enough" data as baseline for future rocket designs. Currently, it consists of a data input sheet, a rocket initial sizing tool, and weight analysis tool. Contributions from those with expertise or interest in rocketry are highly encouraged to enhance its capabilities.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>27/08/2025, 21:01 UTC+7</t>
+  </si>
+  <si>
+    <t>1. Information update on "Le Intro"</t>
+  </si>
+  <si>
+    <t>[1] = R. A. Braeunig, “Rocket propellants,” Rocket and Space Technology, 2008. http://www.braeunig.us/space/propel.htm (accessed Mar. 07, 2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APCP×PBAN ([UwU], [1]) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">APCP×HTPB ([UwU], [1]) </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">References: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[UwU], [OwO], [1], [2]</t>
+    </r>
+  </si>
+  <si>
+    <t>[2] = D. K. Huzel and D. H. Huang, “Design of Liquid Propellant Rocket Engines Second edition,” NASA Technical Reports Server (NTRS), Jan. 01, 1967. https://ntrs.nasa.gov/citations/19710019929</t>
+  </si>
+  <si>
+    <t>Stage delta-v</t>
+  </si>
+  <si>
+    <t>STAGES</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>DIMENSIONS</t>
+  </si>
+  <si>
+    <t>Stage diameter</t>
+  </si>
+  <si>
+    <t>Engine layout</t>
+  </si>
+  <si>
+    <t>1. Geometry, owo~!</t>
+  </si>
+  <si>
+    <t>Jethro Hotasi Sinaga, S.T.</t>
+  </si>
+  <si>
+    <t>1. Switched Gemoetry and Weight Analysis place in the workflow (Excel: L –&gt; R)
+2.  Revised a contributor's title</t>
+  </si>
+  <si>
+    <t>22/09/2026, 15:04 UTC+7</t>
+  </si>
+  <si>
+    <t>Engine number</t>
+  </si>
+  <si>
+    <t>PROPORTION</t>
+  </si>
+  <si>
+    <t>Interstage fairing</t>
+  </si>
+  <si>
+    <t>Computer stuff</t>
+  </si>
+  <si>
+    <t>Engine</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Sub-data</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>DRAWING SIZE</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>DO NOT TOUCH THE FIRST TWO COLUMNS!!! Insert fuel type in the fuel columns and subsequently its specific impulse in the respective columns. When one isn't available, approximate SLIsp = 0.667*VacIsp or inversely VacIsp = 1.5*SLIsp</t>
+  </si>
+  <si>
+    <t>MMH only (NASA OMS)</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>Cruciform</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>Circle w/ middle</t>
+  </si>
+  <si>
+    <t>Grid (F9 before Block 5)</t>
+  </si>
+  <si>
+    <t>Linear</t>
+  </si>
+  <si>
+    <t>Paper size</t>
+  </si>
+  <si>
+    <t>Width (mm)</t>
+  </si>
+  <si>
+    <t>Height (mm)</t>
+  </si>
+  <si>
+    <t>2A0</t>
+  </si>
+  <si>
+    <t>A0</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>Scale to reality</t>
+  </si>
+  <si>
+    <t>4A0</t>
+  </si>
+  <si>
+    <t> 841</t>
+  </si>
+  <si>
+    <t> 594</t>
+  </si>
+  <si>
+    <t> 420</t>
+  </si>
+  <si>
+    <t> 297</t>
+  </si>
+  <si>
+    <t> 210</t>
+  </si>
+  <si>
+    <t> 148</t>
+  </si>
+  <si>
+    <t>Assumed ideal single-stage delta-v requirement</t>
+  </si>
+  <si>
+    <t>Drawing style</t>
+  </si>
+  <si>
+    <t>American (third-angle)</t>
+  </si>
+  <si>
+    <t>European (first-angle)</t>
+  </si>
+  <si>
+    <t>Total height</t>
+  </si>
+  <si>
+    <t>Per-stage height</t>
+  </si>
+  <si>
+    <t>Payload (fairing)</t>
+  </si>
+  <si>
+    <t>Insert numbers in yellow-tinted cells. The initial geometry will be shown in the chart aside the inputs.</t>
+  </si>
+  <si>
+    <t>1. Housekeeping
+2. Sortation of features in "Le Intro"
+3. Further progress on geometry
+4. Revised a contributor's position</t>
+  </si>
+  <si>
+    <t>* = (Co-)Authors Abbreviation Index
+Enter current work position or schooling institution, using official English name. Company names must be the legal one, not just the brand
+If you can't disclose where you work (Academic institution MUST be disclosed), fill with [LE SECRET ONHONHON~]</t>
+  </si>
+  <si>
+    <t>23/09/2026, 22:53 UTC+7</t>
+  </si>
+  <si>
+    <t>Some Rocket Maker Weird Thing (SomRMWT) - Alpha v0.4.rev1 - 23/09/2026</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Yes, this is real. Yes, I'm bored. No, I do have a life." </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+– Muhammad Naufal Afif, 11/01/2025</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -742,165 +1578,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Follow the stated instruction for each spreadsheet
+      <t xml:space="preserve">Follow the stated instruction for each spreadsheet. 
 </t>
-    </r>
-  </si>
-  <si>
-    <t>1. Added to-do list in Intro page
-2. Revised wording in Intro page</t>
-  </si>
-  <si>
-    <t>12/01/2025,15:01 UTC+7</t>
-  </si>
-  <si>
-    <t>13/01/2025, 05:18 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Added expected features</t>
-  </si>
-  <si>
-    <t>APCP</t>
-  </si>
-  <si>
-    <t>HTPB/Paraffin</t>
-  </si>
-  <si>
-    <t>LOX/HTPB</t>
-  </si>
-  <si>
-    <t>N2O4/MMH</t>
-  </si>
-  <si>
-    <t>N2O4/UDMH×N2H4
-(Aerozine 50)</t>
-  </si>
-  <si>
-    <t>N2O4/UDMH</t>
-  </si>
-  <si>
-    <t>Black powder</t>
-  </si>
-  <si>
-    <t>1. Uploaded file to Github for further collaboration</t>
-  </si>
-  <si>
-    <t>13/01/2025, 11:40 UTC+7</t>
-  </si>
-  <si>
-    <t>13/01/2025, 11:41 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Revised Github readme, therefore intro spreadsheet</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Features to be Added
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Must Haves Before Entering Beta Stage (Essential Components): </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1. Weight Analysis
-     2. Engine Performance (complete with thrust chart maker)
-          a. Solid Propellant 
-          b. Liquid Propellant
-     3. Mission Planner Using Designed Rocket's Parameters
-     4. de Laval Nozzle Maker</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">     5. Benchmarking Against Similar Rockets
-     6. Aerodynamic Analysis</t>
-    </r>
-  </si>
-  <si>
-    <t>CO-AUTHORS! PLEASE FILL IN LOG AFTER EDITING! UNLESS MAKING A NEW VERSION, UNLISTED CHANGES ARE NOT RECOGNISED AND WILL BE RECTIFIED!!!</t>
-  </si>
-  <si>
-    <t>[REP]</t>
-  </si>
-  <si>
-    <t>[TIO]</t>
-  </si>
-  <si>
-    <t>Ir. Toto Indriyanto, M.Sc., Ph.D.</t>
-  </si>
-  <si>
-    <t>Lecturer
-Aerospace Engineering Study Program, Faculty of Mechanic and Aerospace Engineering
-Institut Teknologi Bandung</t>
-  </si>
-  <si>
-    <t>Dr. Eng. Ridanto Eko Poetro, S.T, M.Sc.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"Yes, this is real. Yes, I'm bored. No, I do have a life." </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
--Muhammad Naufal Afif, 11/01/2025</t>
     </r>
   </si>
   <si>
@@ -935,12 +1614,14 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>1. Rocket Geometry Drawer (a la Taufiq Mulyanto's AISAT)
+      <t>1. Benchmarking Against Competitors
      2. Payload Maker
      3. Engine Performance (complete with thrust chart maker)
           a. Hybrid Propellant 
      4. Trajectory Visualiser (integrated to Mission Planner)
-     5. Cost Analysis</t>
+     5. Cost Analysis
+     6. Further breakdown as standalone Python/Rust program
+     7. Aerodynamic Analysis</t>
     </r>
     <r>
       <rPr>
@@ -956,279 +1637,19 @@
     </r>
   </si>
   <si>
-    <t>13/01/2025, 11:51 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Some formatting changes to intro spreadsheet and or Github readme</t>
-  </si>
-  <si>
-    <t>Rocket Name</t>
-  </si>
-  <si>
-    <t>Expected Stages</t>
-  </si>
-  <si>
-    <t>Secondary Mission</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What kind of mission? </t>
-  </si>
-  <si>
-    <t>Primary Mission</t>
-  </si>
-  <si>
-    <t>Tertiary Mission</t>
-  </si>
-  <si>
-    <t>Mission #4</t>
-  </si>
-  <si>
-    <t>Mission #5</t>
-  </si>
-  <si>
-    <t>Mission #6</t>
-  </si>
-  <si>
-    <t>Mission #7</t>
-  </si>
-  <si>
-    <t>Mission #8</t>
-  </si>
-  <si>
-    <t>Mission #9</t>
-  </si>
-  <si>
-    <t>Mission #10</t>
-  </si>
-  <si>
-    <t>Expected Rocket Diameter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What kind of orbit? </t>
-  </si>
-  <si>
-    <t>Expected semi-major axis</t>
-  </si>
-  <si>
-    <t>Easy enough. Just insert your data in the yellow-tinted cells, also the orange one if you're feeling frisky since those are optional. You can add more missions if you like. All other sheets refer to data inputed here</t>
-  </si>
-  <si>
-    <t>Assumed ideal single stage delta-v requirement</t>
-  </si>
-  <si>
-    <t>Expected gimbal angle</t>
-  </si>
-  <si>
-    <t>Expected mission orbit inclination</t>
-  </si>
-  <si>
-    <t>Expected Rocket Size (NASA)</t>
-  </si>
-  <si>
-    <t>Smoli (0 - 2000 kg)</t>
-  </si>
-  <si>
-    <t>Imouto (2000 - 20000 kg)</t>
-  </si>
-  <si>
-    <t>Beeg (20000 - 50000 lkg)</t>
-  </si>
-  <si>
-    <t>CHONKER (&gt; 50000 kg)</t>
-  </si>
-  <si>
-    <t>MEO</t>
-  </si>
-  <si>
-    <t>Interplanetary (to Sun)</t>
-  </si>
-  <si>
-    <t>Expected primary launch site latitude</t>
-  </si>
-  <si>
-    <t>Circular</t>
-  </si>
-  <si>
-    <t>Eliptical</t>
-  </si>
-  <si>
-    <t>Interplanetary (away from Sun)</t>
-  </si>
-  <si>
-    <t>Not applicable</t>
-  </si>
-  <si>
-    <t>Expected secondary launch site latitude</t>
-  </si>
-  <si>
-    <t>Total delta-v needed</t>
-  </si>
-  <si>
-    <t>(Boolean)</t>
-  </si>
-  <si>
-    <t>DO NOT EDIT THIS TABLE!!!</t>
-  </si>
-  <si>
-    <t>Expected Rocket Statistics</t>
-  </si>
-  <si>
-    <t>Average payload size</t>
-  </si>
-  <si>
-    <t>Average launch site inclination</t>
-  </si>
-  <si>
-    <t>Average total delta-v requirement</t>
-  </si>
-  <si>
-    <t>degrees</t>
-  </si>
-  <si>
-    <t>m.s^-1</t>
-  </si>
-  <si>
-    <t>ROwOcket</t>
-  </si>
-  <si>
-    <t>PRELIMINARY ROCKET STATS</t>
-  </si>
-  <si>
-    <t>13/01/2025, 19:21 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Data input</t>
-  </si>
-  <si>
-    <t>HOW TO TABLES</t>
-  </si>
-  <si>
-    <t>Ctrl+; and then Ctrl+Shift+; on the date and time cell before inserting your local time zone. Pick your abbreviation (that can be set on the orange table). State in a numbered list concisely what you've done. Copy your Github commits here if you came from there</t>
-  </si>
-  <si>
-    <t>1. Initial sizing sheet now interconnected with data input data
-2. Additional details on how to input logs
-3. Some more statistics on initial sizing</t>
-  </si>
-  <si>
-    <t>* = (Co-)Authors Abbreviation Index
-Enter current work position or schooling institution, using official English name. Company names must be the legal one, not just the brand
-If you can't disclose where you work (Study institution MUST be disclosed), fill with [LE SECRET ONHONHON~]</t>
-  </si>
-  <si>
-    <t>Some Rocket Maker Weird Thing (SomRMWT) - Alpha v0.2 - 13/01/2025</t>
-  </si>
-  <si>
-    <t>Single-stage delta-v for mission</t>
-  </si>
-  <si>
-    <t>LEO (ISS mission mostly)</t>
-  </si>
-  <si>
-    <t>Insert numbers in yellow-tinted cells. Boosters not supported yet, nor coasting</t>
-  </si>
-  <si>
-    <t>Average single-stage ideal delta-v</t>
-  </si>
-  <si>
-    <t>Translunar (assuming LEO parking orbit)</t>
-  </si>
-  <si>
-    <t>Trans-Mars (assuming LEO parking orbit)</t>
-  </si>
-  <si>
-    <t>NOR THIS ONE!!!</t>
-  </si>
-  <si>
-    <t>V: Orbit? | -&gt; Orbit type?</t>
-  </si>
-  <si>
-    <t>14/01/2025, 14:13 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Delta-v calculation in input sheet
-2. Started work on the orbital calculation for input (single-stage to desired orbit)</t>
-  </si>
-  <si>
-    <t>[JHS]</t>
-  </si>
-  <si>
-    <t>Jethro Hotasi Sinaga</t>
-  </si>
-  <si>
-    <t>Parabolic</t>
-  </si>
-  <si>
-    <t>Expected (periapsis) radius</t>
-  </si>
-  <si>
-    <t>GEO/GTO</t>
-  </si>
-  <si>
-    <t>Hyperbolic (assuming a 1 km/s speed)</t>
-  </si>
-  <si>
-    <t>Desired Rocket Payload Ratio (0 -1)</t>
-  </si>
-  <si>
-    <t>Desired propellant mass fraction (0 - 1)</t>
-  </si>
-  <si>
-    <t>Desired dry mass ratio (0 - 1)</t>
-  </si>
-  <si>
-    <t>Liftoff weight</t>
-  </si>
-  <si>
-    <t>14/01/2025, 21:18 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Finally made data input work
-2. Proper initial sizing, about damn time</t>
-  </si>
-  <si>
-    <t>15/01/2025, 10:59 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Improved data input</t>
-  </si>
-  <si>
-    <t>16/01/2025, 08:51 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Improved initial sizing, now with Python!
-2. Put initial sizing data as pandas dataframe</t>
-  </si>
-  <si>
-    <t>Average orbit inclination</t>
-  </si>
-  <si>
-    <t>16/01/2025, 13:08 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Improved needed delta-v budget calculations</t>
-  </si>
-  <si>
-    <t>Benedict Julian Zefanya Batubara</t>
-  </si>
-  <si>
-    <t>[BJB]</t>
-  </si>
-  <si>
-    <t>16/01/2025, 16:18 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Uploaded revision to GitHub
-      a.Officially added co-authors
-     b. Refined initial sizing algorithm</t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">
+      <t xml:space="preserve">Features to be Added
 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Must Haves Before Entering Beta Stage (Essential Components): </t>
     </r>
     <r>
       <rPr>
@@ -1239,7 +1660,40 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>What Even Is This?</t>
+      <t xml:space="preserve">
+     </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1. Data Input</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(DONE!)</t>
     </r>
     <r>
       <rPr>
@@ -1250,23 +1704,29 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-SomRMWT is a rocket designer built using Excel and coded partially in Python, designed for hobby rocketry, academic purposes as teaching tool, or conceptual rocket designs. Started when Muhammad Naufal Afif was bored on his sixth year studying aerospace engineering, it provides "good enough" data as baseline for future rocket designs. Currently, it consists of a data input sheet and a rocket initial sizing tool. Contributions from those with expertise or interest in rocketry are highly encouraged to enhance its capabilities.
-</t>
+     </t>
     </r>
-  </si>
-  <si>
-    <t>Maximum total delta-v requirement</t>
-  </si>
-  <si>
-    <t>Fulfils average delta-v?</t>
-  </si>
-  <si>
-    <t>Fulfils max delta-v?</t>
-  </si>
-  <si>
-    <t>^ DO NOT EVER TOUCH THIS CELL!!!</t>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2. Initial Sizing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -1276,7 +1736,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">References: </t>
+      <t>(DONE!)</t>
     </r>
     <r>
       <rPr>
@@ -1286,12 +1746,25 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[OwO]</t>
+      <t xml:space="preserve">
+     3. Rocket Geometry Drawer (a la Taufiq Mulyanto's AISAT)
+     4. Weight Analysis
+     5. Engine Performance (complete with thrust chart maker)
+           a. Solid Propellant 
+           b. Liquid Propellant
+     6. Mission Planner Using RocketPy</t>
     </r>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">References: </t>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -1301,80 +1774,18 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[OwO]</t>
+      <t xml:space="preserve">     7. de Laval Nozzle Maker</t>
     </r>
-  </si>
-  <si>
-    <t>17/01/2025, 16:50 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Improved expected rocket statistics in data input: Now With Python!
-2. Improved log tracking
-3. Improved initial sizing</t>
-  </si>
-  <si>
-    <t>Pak Hendri
-+6281321210645</t>
-  </si>
-  <si>
-    <t>DO NOT EVER TOUCH THIS CELL!!! -&gt;</t>
-  </si>
-  <si>
-    <t>Optimise rocket?</t>
-  </si>
-  <si>
-    <t>Optimised delta-v budget</t>
-  </si>
-  <si>
-    <t>Calculated delta-v budget</t>
-  </si>
-  <si>
-    <t>22/01/2025, 16:30 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Revised Python code for data sizing
-2. Switched Python-enabled cell from being Python objects to become Excel values</t>
-  </si>
-  <si>
-    <t>1. "Goal seek" optimisation for rocket initial sizing</t>
-  </si>
-  <si>
-    <t>Graduate
-Aerospace Engineering Study Program, Faculty of Mechanic and Aerospace Engineering
-Institut Teknologi Bandung</t>
-  </si>
-  <si>
-    <t>20/08/2025, 14:20 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Revised lead contributor's position</t>
-  </si>
-  <si>
-    <t>Muhammad Naufal Afif, S.T.</t>
-  </si>
-  <si>
-    <t>[DAS]</t>
-  </si>
-  <si>
-    <t>David Soegijanto, S.T.</t>
-  </si>
-  <si>
-    <t>Graduate Student
-Aerospace Engineering Study Program, Faculty of Mechanic and Aerospace Engineering
-Institut Teknologi Bandung</t>
-  </si>
-  <si>
-    <t>21/08/2025, 21:42 UTC+7</t>
-  </si>
-  <si>
-    <t>1. Added new contributor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1456,6 +1867,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF202122"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202122"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1495,7 +1935,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1642,11 +2082,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="1" diagonalDown="1">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1660,9 +2112,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1762,6 +2211,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1770,9 +2253,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1783,10 +2263,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1798,11 +2275,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="93">
+  <dxfs count="113">
     <dxf>
       <font>
         <color theme="0"/>
@@ -2052,7 +2604,13 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -2067,162 +2625,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right style="thin">
@@ -2260,7 +2663,7 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -2270,370 +2673,8 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2648,6 +2689,97 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3282,6 +3414,715 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -3492,7 +4333,7 @@
     <v t="s">Fuel type?</v>
     <v t="s">Fuel</v>
     <v t="s">...</v>
-    <v t="s">Delta-v</v>
+    <v t="s">Stage delta-v</v>
     <v t="s">Burn time</v>
     <v t="s">Thrust</v>
     <v t="s">Total impulse</v>
@@ -3504,11 +4345,11 @@
     <v t="r">0</v>
     <v t="r">0</v>
     <v t="s">...</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
     <v>1</v>
     <v>1</v>
     <v>9654.8938460562986</v>
@@ -3552,11 +4393,11 @@
     <v t="r">0</v>
     <v t="r">0</v>
     <v t="s">...</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
     <v t="s">...</v>
     <v t="s">...</v>
     <v t="s">...</v>
@@ -3576,11 +4417,11 @@
     <v t="r">0</v>
     <v t="r">0</v>
     <v t="s">...</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
     <v>7</v>
     <v>7</v>
     <v>9654893846.0563145</v>
@@ -3588,11 +4429,11 @@
     <v t="r">0</v>
     <v t="r">0</v>
     <v t="s">...</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
     <v>8</v>
     <v>8</v>
     <v>96548938460.563171</v>
@@ -3600,11 +4441,11 @@
     <v t="r">0</v>
     <v t="r">0</v>
     <v t="s">...</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
     <v>9</v>
     <v>9</v>
     <v>965489384605.63196</v>
@@ -3612,11 +4453,11 @@
     <v t="r">0</v>
     <v t="r">0</v>
     <v t="s">...</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
     <v>10</v>
     <v>10</v>
     <v>9654893846056.3223</v>
@@ -3624,17 +4465,17 @@
     <v t="r">0</v>
     <v t="r">0</v>
     <v t="s">...</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
-    <v t="r">4</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
+    <v t="r">5</v>
   </a>
 </arrayData>
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <fb>0</fb>
     <v>2</v>
@@ -3657,6 +4498,13 @@
     <v>2</v>
     <v>3</v>
   </rv>
+  <rv s="4">
+    <v>2cfac00fc58249caa602d0ed80ed49b2</v>
+    <v>[Errno 2] No such file or directory: '/mnt/file_upload//Python Dependencies//init_sizing.py'</v>
+    <v>FileNotFoundError</v>
+    <v>18</v>
+    <v>1</v>
+  </rv>
   <rv s="0">
     <fb>0</fb>
     <v>6</v>
@@ -3667,7 +4515,7 @@
   <rv s="2">
     <v>DataFrame</v>
     <v>5</v>
-    <v>5</v>
+    <v>6</v>
   </rv>
   <rv s="3">
     <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
@@ -3676,14 +4524,14 @@
 0   Payload  9.654894e+03       None       None                None   
 1         1  9.654894e+03         NO      Solid        HTPB (LAPAN)   
 2         2  9.654894e+04         NO   ...</v>
-    <v>6</v>
+    <v>7</v>
     <v>3</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_formattednumber">
     <k n="_Format" t="spb"/>
   </s>
@@ -3701,6 +4549,13 @@
     <k n="Python_str" t="s"/>
     <k n="preview" t="r"/>
     <k n="_Provider" t="spb"/>
+  </s>
+  <s t="_error">
+    <k n="correlationId" t="s"/>
+    <k n="errorMessage" t="s"/>
+    <k n="errorName" t="s"/>
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
   </s>
 </rvStructures>
 </file>
@@ -3788,28 +4643,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02AC8A23-A629-49DA-9612-16991BC7E0CF}" name="TheDropdownMenuTable_DataInput" displayName="TheDropdownMenuTable_DataInput" ref="B44:E51" totalsRowShown="0" headerRowBorderDxfId="92" tableBorderDxfId="91" totalsRowBorderDxfId="90">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02AC8A23-A629-49DA-9612-16991BC7E0CF}" name="TheDropdownMenuTable_DataInput" displayName="TheDropdownMenuTable_DataInput" ref="B44:E51" totalsRowShown="0" headerRowBorderDxfId="70" tableBorderDxfId="69" totalsRowBorderDxfId="68">
   <autoFilter ref="B44:E51" xr:uid="{02AC8A23-A629-49DA-9612-16991BC7E0CF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{37C26436-216C-4530-992E-9414322F8925}" name="Expected Rocket Size (NASA)" dataDxfId="89"/>
-    <tableColumn id="2" xr3:uid="{F7CE6833-F045-4505-BBB1-32CEAA513166}" name="What kind of mission? " dataDxfId="88"/>
-    <tableColumn id="4" xr3:uid="{2173F227-01D3-4B33-A0D6-EBF6EFF1FD1E}" name="Single-stage delta-v for mission" dataDxfId="87">
+    <tableColumn id="1" xr3:uid="{37C26436-216C-4530-992E-9414322F8925}" name="Expected Rocket Size (NASA)" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{F7CE6833-F045-4505-BBB1-32CEAA513166}" name="What kind of mission? " dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{2173F227-01D3-4B33-A0D6-EBF6EFF1FD1E}" name="Single-stage delta-v for mission" dataDxfId="65">
       <calculatedColumnFormula>((9.81*6378000^3)/(6378000+400000))^0.5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1648E833-C30F-405E-9AAA-C8448639848B}" name="What kind of orbit? " dataDxfId="86"/>
+    <tableColumn id="3" xr3:uid="{1648E833-C30F-405E-9AAA-C8448639848B}" name="What kind of orbit? " dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1B69BB83-84D8-46C0-A587-691AAF9243B4}" name="AuthorTable" displayName="AuthorTable" ref="F7:H29" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+  <autoFilter ref="F7:H29" xr:uid="{1B69BB83-84D8-46C0-A587-691AAF9243B4}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F8:H29">
+    <sortCondition ref="F7:F29"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{67C7794C-1BBF-4F6D-905A-6E2F5D7C3549}" name="Abbr." dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{BCD48711-8DAF-4F81-B9B1-A9AE6C37DFED}" name="Name" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{643541DB-6FC1-4211-AADD-E6164D95190E}" name="Work/School" dataDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{973BA3E3-292E-4F9B-8FC4-4172FB53A2F9}" name="DataInputTable" displayName="DataInputTable" ref="B13:L24" totalsRowShown="0" headerRowDxfId="85" headerRowBorderDxfId="84" tableBorderDxfId="83" totalsRowBorderDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{973BA3E3-292E-4F9B-8FC4-4172FB53A2F9}" name="DataInputTable" displayName="DataInputTable" ref="B13:L24" totalsRowShown="0" headerRowDxfId="63" headerRowBorderDxfId="62" tableBorderDxfId="61" totalsRowBorderDxfId="60">
   <autoFilter ref="B13:L24" xr:uid="{973BA3E3-292E-4F9B-8FC4-4172FB53A2F9}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{ABF0C372-0E46-4662-A2C0-2A30F2555CDC}" name="Attribute" dataDxfId="81"/>
-    <tableColumn id="2" xr3:uid="{8A769E52-51EA-4931-B79B-BA85D1C4A8EC}" name="Primary Mission" dataDxfId="80"/>
-    <tableColumn id="3" xr3:uid="{5C515417-3844-49FD-B0B2-8189E42BCC26}" name="Secondary Mission" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{7F8A43EC-A596-4550-A14C-5415BCDA1B52}" name="Tertiary Mission" dataDxfId="78">
+    <tableColumn id="1" xr3:uid="{ABF0C372-0E46-4662-A2C0-2A30F2555CDC}" name="Attribute" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{8A769E52-51EA-4931-B79B-BA85D1C4A8EC}" name="Primary Mission" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{5C515417-3844-49FD-B0B2-8189E42BCC26}" name="Secondary Mission" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{7F8A43EC-A596-4550-A14C-5415BCDA1B52}" name="Tertiary Mission" dataDxfId="56">
       <calculatedColumnFormula>IF(
     ISBLANK(E10),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -3839,7 +4709,7 @@
                )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{59EA6F45-44F7-407D-836B-D7315DFC7AB9}" name="Mission #4" dataDxfId="77">
+    <tableColumn id="5" xr3:uid="{59EA6F45-44F7-407D-836B-D7315DFC7AB9}" name="Mission #4" dataDxfId="55">
       <calculatedColumnFormula>IF(
     ISBLANK(F9),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -3869,7 +4739,7 @@
                )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{65777FC9-5529-46FE-A286-35373E1FB94F}" name="Mission #5" dataDxfId="76">
+    <tableColumn id="6" xr3:uid="{65777FC9-5529-46FE-A286-35373E1FB94F}" name="Mission #5" dataDxfId="54">
       <calculatedColumnFormula>IF(
     ISBLANK(G10),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -3888,8 +4758,8 @@
     )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3A5B2374-D007-4C77-BB09-29980BD9AB9B}" name="Mission #6" dataDxfId="75"/>
-    <tableColumn id="8" xr3:uid="{2FC93AA1-806F-4C30-82A3-8A6E6F18536E}" name="Mission #7" dataDxfId="74">
+    <tableColumn id="7" xr3:uid="{3A5B2374-D007-4C77-BB09-29980BD9AB9B}" name="Mission #6" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{2FC93AA1-806F-4C30-82A3-8A6E6F18536E}" name="Mission #7" dataDxfId="52">
       <calculatedColumnFormula>IF(
     ISBLANK(I10),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -3908,7 +4778,7 @@
     )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{388BEDD1-3800-465E-8D1C-7B79AA268D8D}" name="Mission #8" dataDxfId="73">
+    <tableColumn id="9" xr3:uid="{388BEDD1-3800-465E-8D1C-7B79AA268D8D}" name="Mission #8" dataDxfId="51">
       <calculatedColumnFormula>IF(
     ISBLANK(J10),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -3927,7 +4797,7 @@
     )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{AE463282-A8F6-4BEA-9979-CB917AC39418}" name="Mission #9" dataDxfId="72">
+    <tableColumn id="10" xr3:uid="{AE463282-A8F6-4BEA-9979-CB917AC39418}" name="Mission #9" dataDxfId="50">
       <calculatedColumnFormula>IF(
     ISBLANK(K10),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -3946,7 +4816,7 @@
     )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{CD8B480D-C681-479A-916C-0B9C217F96A0}" name="Mission #10" dataDxfId="71">
+    <tableColumn id="11" xr3:uid="{CD8B480D-C681-479A-916C-0B9C217F96A0}" name="Mission #10" dataDxfId="49">
       <calculatedColumnFormula>IF(
     ISBLANK(L10),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -3971,56 +4841,56 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B21E3321-0EF2-4007-9DF9-C3BD57AFB99F}" name="DeltaVCalculator_InitialSizing" displayName="DeltaVCalculator_InitialSizing" ref="B54:F61" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67" totalsRowBorderDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B21E3321-0EF2-4007-9DF9-C3BD57AFB99F}" name="DeltaVCalculator_InitialSizing" displayName="DeltaVCalculator_InitialSizing" ref="B54:F61" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
   <autoFilter ref="B54:F61" xr:uid="{B21E3321-0EF2-4007-9DF9-C3BD57AFB99F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{65EC6A74-7A03-4795-9F14-DB1783F29F1A}" name="V: Orbit? | -&gt; Orbit type?" dataDxfId="65"/>
-    <tableColumn id="2" xr3:uid="{2B4D7578-F4F9-46AF-A8F9-47865D4A2E63}" name="Circular" dataDxfId="64">
+    <tableColumn id="1" xr3:uid="{65EC6A74-7A03-4795-9F14-DB1783F29F1A}" name="V: Orbit? | -&gt; Orbit type?" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{2B4D7578-F4F9-46AF-A8F9-47865D4A2E63}" name="Circular" dataDxfId="42">
       <calculatedColumnFormula>D45</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{311BCEAB-D978-4E5A-A256-C5F3952C6E68}" name="Eliptical" dataDxfId="63">
+    <tableColumn id="3" xr3:uid="{311BCEAB-D978-4E5A-A256-C5F3952C6E68}" name="Eliptical" dataDxfId="41">
       <calculatedColumnFormula>((9.81*6378000^2)*((2/(_xlfn.AGGREGATE(5,3,$C$17:$L$17)))-(1/_xlfn.AGGREGATE(5,3,$C$18:$L$18))))^0.5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{AB7A6491-CE84-490E-B0FB-FD5016756293}" name="Parabolic" dataDxfId="62">
+    <tableColumn id="4" xr3:uid="{AB7A6491-CE84-490E-B0FB-FD5016756293}" name="Parabolic" dataDxfId="40">
       <calculatedColumnFormula>(2*(9.81*6378000^2)/(6378000+400000))^0.5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{81DC2721-E2FD-4C7D-BC37-F30D428E8630}" name="Hyperbolic (assuming a 1 km/s speed)" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{81DC2721-E2FD-4C7D-BC37-F30D428E8630}" name="Hyperbolic (assuming a 1 km/s speed)" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3F99EFFE-4ED4-4BEA-986A-0303615C7CC1}" name="LeInitialSizingTable" displayName="LeInitialSizingTable" ref="A9:N20" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57" totalsRowBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3F99EFFE-4ED4-4BEA-986A-0303615C7CC1}" name="LeInitialSizingTable" displayName="LeInitialSizingTable" ref="A9:N20" totalsRowShown="0" headerRowDxfId="112" dataDxfId="110" headerRowBorderDxfId="111" tableBorderDxfId="109" totalsRowBorderDxfId="108">
   <autoFilter ref="A9:N20" xr:uid="{3F99EFFE-4ED4-4BEA-986A-0303615C7CC1}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{D376856A-4962-4798-BB88-4A0DA8662518}" name="Stage" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{F93C9EE3-1BFB-4341-84EA-2A1AD8B0D50D}" name="Final mass" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{8913E803-65F3-4F8E-AB66-F6638A22A5B3}" name="In vacuum?" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{337A64D6-17B1-475C-A652-6D66D906B4B6}" name="Fuel type?" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{8390B592-9AAD-49E4-9CCF-29A77EF82BE1}" name="Fuel" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{E8C050E1-AD7D-4BC2-9663-F725C55D036F}" name="Specific impulse" dataDxfId="50">
+    <tableColumn id="1" xr3:uid="{D376856A-4962-4798-BB88-4A0DA8662518}" name="Stage" dataDxfId="107"/>
+    <tableColumn id="2" xr3:uid="{F93C9EE3-1BFB-4341-84EA-2A1AD8B0D50D}" name="Final mass" dataDxfId="106"/>
+    <tableColumn id="3" xr3:uid="{8913E803-65F3-4F8E-AB66-F6638A22A5B3}" name="In vacuum?" dataDxfId="105"/>
+    <tableColumn id="4" xr3:uid="{337A64D6-17B1-475C-A652-6D66D906B4B6}" name="Fuel type?" dataDxfId="104"/>
+    <tableColumn id="5" xr3:uid="{8390B592-9AAD-49E4-9CCF-29A77EF82BE1}" name="Fuel" dataDxfId="103"/>
+    <tableColumn id="6" xr3:uid="{E8C050E1-AD7D-4BC2-9663-F725C55D036F}" name="Specific impulse" dataDxfId="102">
       <calculatedColumnFormula>IF(LeInitialSizingTable[[#This Row],[Fuel type?]] = "Solid", INDEX(IF(LeInitialSizingTable[[#This Row],[In vacuum?]] = "YES", TheDropdownMenuTable_InitialSizing[Isp (solid, vacuum)], TheDropdownMenuTable_InitialSizing[Isp (solid, SL)]), MATCH(LeInitialSizingTable[[#This Row],[Fuel]], TheDropdownMenuTable_InitialSizing[Fuel (solid)], 0)), IF(LeInitialSizingTable[[#This Row],[Fuel type?]] = "Liquid", INDEX(IF(LeInitialSizingTable[[#This Row],[In vacuum?]] = "YES", TheDropdownMenuTable_InitialSizing[Isp (liquid, vacuum)], TheDropdownMenuTable_InitialSizing[Isp (liquid, SL)]), MATCH(LeInitialSizingTable[[#This Row],[Fuel]], TheDropdownMenuTable_InitialSizing[Fuel (liquid)], 0)), INDEX(IF(LeInitialSizingTable[[#This Row],[In vacuum?]] = "YES", TheDropdownMenuTable_InitialSizing[Isp (IDFK, vacuum)], TheDropdownMenuTable_InitialSizing[Isp (IDFK, SL)]), MATCH(LeInitialSizingTable[[#This Row],[Fuel]], TheDropdownMenuTable_InitialSizing[Fuel (IDFK)], 0))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{9383E0D6-DB61-4034-B434-F40101757504}" name="Stage dry mass" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{2769C384-836C-44A2-9BDE-B30501571738}" name="Propellant mass" dataDxfId="48">
+    <tableColumn id="7" xr3:uid="{9383E0D6-DB61-4034-B434-F40101757504}" name="Stage dry mass" dataDxfId="101"/>
+    <tableColumn id="8" xr3:uid="{2769C384-836C-44A2-9BDE-B30501571738}" name="Propellant mass" dataDxfId="100">
       <calculatedColumnFormula>(LeInitialSizingTable[[#This Row],[Stage dry mass]]*0.875)/(1-0.875)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C25A4253-7F52-43B4-AA0F-6A0DB8190EB4}" name="Wet mass" dataDxfId="47">
+    <tableColumn id="9" xr3:uid="{C25A4253-7F52-43B4-AA0F-6A0DB8190EB4}" name="Wet mass" dataDxfId="99">
       <calculatedColumnFormula>LeInitialSizingTable[[#This Row],[Propellant mass]] + LeInitialSizingTable[[#This Row],[Stage dry mass]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F280A7DF-D77D-4969-9F58-A44E97EA414C}" name="Delta-v" dataDxfId="46">
+    <tableColumn id="10" xr3:uid="{F280A7DF-D77D-4969-9F58-A44E97EA414C}" name="Stage delta-v" dataDxfId="98">
       <calculatedColumnFormula>9.81*LeInitialSizingTable[[#This Row],[Specific impulse]]*LN(LeInitialSizingTable[[#This Row],[Wet mass]]/(LeInitialSizingTable[[#This Row],[Stage dry mass]]+LeInitialSizingTable[[#This Row],[Final mass]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AD19E824-0495-4F3E-B0F1-D4A9054E38C6}" name="Burn time" dataDxfId="45"/>
-    <tableColumn id="14" xr3:uid="{C39CD05B-EBD7-4EB7-8B19-26D0DBE94A99}" name="Thrust" dataDxfId="44">
+    <tableColumn id="11" xr3:uid="{AD19E824-0495-4F3E-B0F1-D4A9054E38C6}" name="Burn time" dataDxfId="97"/>
+    <tableColumn id="14" xr3:uid="{C39CD05B-EBD7-4EB7-8B19-26D0DBE94A99}" name="Thrust" dataDxfId="96">
       <calculatedColumnFormula>9.81*LeInitialSizingTable[[#This Row],[Specific impulse]]*(LeInitialSizingTable[[#This Row],[Propellant mass]]/LeInitialSizingTable[[#This Row],[Burn time]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{AFFFA182-C9D2-4A9B-8100-4455137B27EF}" name="Total impulse" dataDxfId="43">
+    <tableColumn id="15" xr3:uid="{AFFFA182-C9D2-4A9B-8100-4455137B27EF}" name="Total impulse" dataDxfId="95">
       <calculatedColumnFormula>LeInitialSizingTable[[#This Row],[Thrust]]*LeInitialSizingTable[[#This Row],[Burn time]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F0E8BA93-AD48-40C6-84C5-0566DD8384A2}" name="Total delta-v" dataDxfId="42">
-      <calculatedColumnFormula>LeInitialSizingTable[[#This Row],[Delta-v]]</calculatedColumnFormula>
+    <tableColumn id="16" xr3:uid="{F0E8BA93-AD48-40C6-84C5-0566DD8384A2}" name="Total delta-v" dataDxfId="94">
+      <calculatedColumnFormula>LeInitialSizingTable[[#This Row],[Stage delta-v]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4028,30 +4898,64 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EF13518-9C68-4392-873C-8B717204DF70}" name="TheDropdownMenuTable_InitialSizing" displayName="TheDropdownMenuTable_InitialSizing" ref="A40:K50" totalsRowShown="0" headerRowDxfId="41" dataDxfId="39" headerRowBorderDxfId="40" tableBorderDxfId="38" totalsRowBorderDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EF13518-9C68-4392-873C-8B717204DF70}" name="TheDropdownMenuTable_InitialSizing" displayName="TheDropdownMenuTable_InitialSizing" ref="A40:K50" totalsRowShown="0" headerRowDxfId="93" dataDxfId="91" headerRowBorderDxfId="92" tableBorderDxfId="90" totalsRowBorderDxfId="89">
   <autoFilter ref="A40:K50" xr:uid="{9EF13518-9C68-4392-873C-8B717204DF70}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{B53D82EE-C966-4662-82CD-7B051C591F23}" name="Vacuum?" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{1F287FF0-02DA-4864-A0EA-D3475D35BA05}" name="Fuel type?" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{2D4CA319-928F-4B2F-8D10-4B07CA0BA891}" name="Fuel (solid)" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{3CA1B53C-5BCD-4573-9218-9CB2B1B49E9F}" name="Isp (solid, vacuum)" dataDxfId="33">
+    <tableColumn id="1" xr3:uid="{B53D82EE-C966-4662-82CD-7B051C591F23}" name="Vacuum?" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{1F287FF0-02DA-4864-A0EA-D3475D35BA05}" name="Fuel type?" dataDxfId="87"/>
+    <tableColumn id="3" xr3:uid="{2D4CA319-928F-4B2F-8D10-4B07CA0BA891}" name="Fuel (solid)" dataDxfId="86"/>
+    <tableColumn id="4" xr3:uid="{3CA1B53C-5BCD-4573-9218-9CB2B1B49E9F}" name="Isp (solid, vacuum)" dataDxfId="85">
       <calculatedColumnFormula>1.5*TheDropdownMenuTable_InitialSizing[[#This Row],[Isp (solid, SL)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C713570A-858E-4AB8-9355-FC886FFD996D}" name="Isp (solid, SL)" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{754AEC55-8326-401C-8F4B-7DD5053E3E02}" name="Fuel (liquid)" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{08A24A14-D47C-4E1F-BA77-20E938CE17A1}" name="Isp (liquid, vacuum)" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{895DD8CC-974E-4FC3-8943-9621F83A88ED}" name="Isp (liquid, SL)" dataDxfId="29"/>
-    <tableColumn id="9" xr3:uid="{EC606D3E-C916-4B91-892A-627311011AB6}" name="Fuel (IDFK)" dataDxfId="28"/>
-    <tableColumn id="10" xr3:uid="{E093D31E-C83D-4E00-BBD0-012867BD73FF}" name="Isp (IDFK, vacuum)" dataDxfId="27">
+    <tableColumn id="5" xr3:uid="{C713570A-858E-4AB8-9355-FC886FFD996D}" name="Isp (solid, SL)" dataDxfId="84"/>
+    <tableColumn id="6" xr3:uid="{754AEC55-8326-401C-8F4B-7DD5053E3E02}" name="Fuel (liquid)" dataDxfId="83"/>
+    <tableColumn id="7" xr3:uid="{08A24A14-D47C-4E1F-BA77-20E938CE17A1}" name="Isp (liquid, vacuum)" dataDxfId="82"/>
+    <tableColumn id="8" xr3:uid="{895DD8CC-974E-4FC3-8943-9621F83A88ED}" name="Isp (liquid, SL)" dataDxfId="81"/>
+    <tableColumn id="9" xr3:uid="{EC606D3E-C916-4B91-892A-627311011AB6}" name="Fuel (IDFK)" dataDxfId="80"/>
+    <tableColumn id="10" xr3:uid="{E093D31E-C83D-4E00-BBD0-012867BD73FF}" name="Isp (IDFK, vacuum)" dataDxfId="79">
       <calculatedColumnFormula>1.5*TheDropdownMenuTable_InitialSizing[[#This Row],[Isp (IDFK, SL)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{74C1F2A4-CF73-40BF-B37D-34BC90E86AD4}" name="Isp (IDFK, SL)" dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{74C1F2A4-CF73-40BF-B37D-34BC90E86AD4}" name="Isp (IDFK, SL)" dataDxfId="78"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{EEE32224-F949-4AFD-BE0A-040D52454BE4}" name="FuelOxRatios" displayName="FuelOxRatios" ref="B53:D67" totalsRowShown="0" headerRowDxfId="77" headerRowBorderDxfId="76" tableBorderDxfId="75" totalsRowBorderDxfId="74">
+  <autoFilter ref="B53:D67" xr:uid="{EEE32224-F949-4AFD-BE0A-040D52454BE4}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{E9C4C0A5-3A39-4D44-BB53-8513C87999CC}" name="Fuel type" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{833C6958-4779-43DB-9343-962FD86B1817}" name="Proportion, fuel" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{C1BD6937-97FF-4570-A063-C51AF695051A}" name="Proportion, oxidiser" dataDxfId="71"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3BF9D88C-D597-4469-BBC5-1E1BE544003E}" name="Table8" displayName="Table8" ref="A5:B10" totalsRowShown="0" headerRowDxfId="38" headerRowBorderDxfId="37" tableBorderDxfId="36" totalsRowBorderDxfId="35">
+  <autoFilter ref="A5:B10" xr:uid="{3BF9D88C-D597-4469-BBC5-1E1BE544003E}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{B8022551-44E3-411F-98AB-60C091A54B7C}" name="Things inputted" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{236F13BD-BCBD-4AD8-A6EF-30B702D55C56}" name="Input value" dataDxfId="33"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{19B77C25-E91F-4FD3-9A2D-C822291D4541}" name="Table9" displayName="Table9" ref="A12:B22" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31" tableBorderDxfId="29" totalsRowBorderDxfId="28">
+  <autoFilter ref="A12:B22" xr:uid="{19B77C25-E91F-4FD3-9A2D-C822291D4541}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{C680718E-51CC-4A21-B851-8F1547F3F0D6}" name="Stage" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{B9B9F106-7248-4641-8549-AE1550AB9F81}" name="Desired thrust-to-weight ratio" dataDxfId="26"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CB9257BB-A782-4818-94CC-AFB62491CBFD}" name="LogTable" displayName="LogTable" ref="A5:D155" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
   <autoFilter ref="A5:D155" xr:uid="{CB9257BB-A782-4818-94CC-AFB62491CBFD}"/>
   <tableColumns count="4">
@@ -4061,21 +4965,6 @@
     <tableColumn id="4" xr3:uid="{0FAD250E-977C-4772-837C-DD97F7AB8A1D}" name="Addition" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1B69BB83-84D8-46C0-A587-691AAF9243B4}" name="AuthorTable" displayName="AuthorTable" ref="F7:H29" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
-  <autoFilter ref="F7:H29" xr:uid="{1B69BB83-84D8-46C0-A587-691AAF9243B4}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F8:H29">
-    <sortCondition ref="F7:F29"/>
-  </sortState>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{67C7794C-1BBF-4F6D-905A-6E2F5D7C3549}" name="Abbr." dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{BCD48711-8DAF-4F81-B9B1-A9AE6C37DFED}" name="Name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{643541DB-6FC1-4211-AADD-E6164D95190E}" name="Work/School" dataDxfId="9"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -4400,55 +5289,53 @@
   <dimension ref="B2:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="90.21875" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="96.77734375" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="42" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
-        <v>139</v>
+    <row r="2" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="97" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B4" s="14" t="s">
-        <v>84</v>
+      <c r="B4" s="13" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="14" t="s">
-        <v>173</v>
+      <c r="B5" s="13" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B6" s="14" t="s">
-        <v>60</v>
+      <c r="B6" s="13" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="14" t="s">
-        <v>45</v>
+      <c r="B7" s="13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="72" x14ac:dyDescent="0.3">
-      <c r="B8" s="14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="B10" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="23" t="s">
-        <v>85</v>
+      <c r="B8" s="13" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="C10" s="32"/>
+    </row>
+    <row r="11" spans="2:3" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="B11" s="22" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="36" x14ac:dyDescent="0.3">
-      <c r="B12" s="24" t="s">
-        <v>78</v>
+      <c r="B12" s="23" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -4468,31 +5355,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="54"/>
+      <c r="B2" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="59"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C7" s="11">
         <v>3</v>
@@ -4500,15 +5387,15 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C9" s="11">
         <v>6</v>
@@ -4516,7 +5403,7 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C10" s="11">
         <v>0.01</v>
@@ -4524,41 +5411,41 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="I13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="L13" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="42" t="s">
         <v>1</v>
       </c>
       <c r="C14" s="11">
@@ -4567,62 +5454,62 @@
       <c r="D14" s="11">
         <v>6000</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="33">
         <v>10000</v>
       </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="43" t="s">
-        <v>92</v>
+      <c r="B15" s="42" t="s">
+        <v>86</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
+        <v>144</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="43" t="s">
-        <v>103</v>
+      <c r="B16" s="42" t="s">
+        <v>97</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
+        <v>110</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="44" t="s">
-        <v>153</v>
+      <c r="B17" s="43" t="s">
+        <v>143</v>
       </c>
       <c r="C17" s="11">
         <v>6771000</v>
@@ -4630,21 +5517,21 @@
       <c r="D17" s="11">
         <v>42164000</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="33">
         <f>0.667*DataInputTable[[#This Row],[Secondary Mission]]</f>
         <v>28123388</v>
       </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="44" t="s">
-        <v>104</v>
+      <c r="B18" s="43" t="s">
+        <v>98</v>
       </c>
       <c r="C18" s="11">
         <v>5000000</v>
@@ -4653,23 +5540,23 @@
         <f>0.667*D17</f>
         <v>28123388</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="33">
         <f>0.667*E17</f>
         <v>18758299.796</v>
       </c>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
     </row>
     <row r="19" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B19" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="40">
+      <c r="B19" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="C19" s="39">
         <f>IF(
     ISBLANK(C16),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -4700,7 +5587,7 @@
 )</f>
         <v>7668.5932308350311</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="39">
         <f>IF(
     ISBLANK(D16),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -4731,7 +5618,7 @@
 )</f>
         <v>10741.65441050474</v>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="36">
         <f>IF(
     ISBLANK(E16),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -4762,7 +5649,7 @@
 )</f>
         <v>10334.196520863028</v>
       </c>
-      <c r="F19" s="37" t="str">
+      <c r="F19" s="36" t="str">
         <f>IF(
     ISBLANK(F16),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -4793,7 +5680,7 @@
 )</f>
         <v>Oh nyo, pwease insert orbit type ÓwÒ</v>
       </c>
-      <c r="G19" s="37" t="str">
+      <c r="G19" s="36" t="str">
         <f>IF(
     ISBLANK(G16),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -4824,7 +5711,7 @@
 )</f>
         <v>Oh nyo, pwease insert orbit type ÓwÒ</v>
       </c>
-      <c r="H19" s="37" t="str">
+      <c r="H19" s="36" t="str">
         <f>IF(
     ISBLANK(H16),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -4855,7 +5742,7 @@
 )</f>
         <v>Oh nyo, pwease insert orbit type ÓwÒ</v>
       </c>
-      <c r="I19" s="37" t="str">
+      <c r="I19" s="36" t="str">
         <f>IF(
     ISBLANK(I16),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -4886,7 +5773,7 @@
 )</f>
         <v>Oh nyo, pwease insert orbit type ÓwÒ</v>
       </c>
-      <c r="J19" s="37" t="str">
+      <c r="J19" s="36" t="str">
         <f>IF(
     ISBLANK(J16),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -4917,7 +5804,7 @@
 )</f>
         <v>Oh nyo, pwease insert orbit type ÓwÒ</v>
       </c>
-      <c r="K19" s="37" t="str">
+      <c r="K19" s="36" t="str">
         <f>IF(
     ISBLANK(K16),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -4948,7 +5835,7 @@
 )</f>
         <v>Oh nyo, pwease insert orbit type ÓwÒ</v>
       </c>
-      <c r="L19" s="37" t="str">
+      <c r="L19" s="36" t="str">
         <f>IF(
     ISBLANK(L16),
     "Oh nyo, pwease insert orbit type ÓwÒ",
@@ -4981,8 +5868,8 @@
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="44" t="s">
-        <v>107</v>
+      <c r="B20" s="43" t="s">
+        <v>100</v>
       </c>
       <c r="C20" s="11">
         <v>4</v>
@@ -4990,20 +5877,20 @@
       <c r="D20" s="11">
         <v>4</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="33">
         <v>4</v>
       </c>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="44" t="s">
-        <v>108</v>
+      <c r="B21" s="43" t="s">
+        <v>101</v>
       </c>
       <c r="C21" s="11">
         <v>0</v>
@@ -5011,20 +5898,20 @@
       <c r="D21" s="11">
         <v>60</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="33">
         <v>0</v>
       </c>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="44" t="s">
-        <v>116</v>
+      <c r="B22" s="43" t="s">
+        <v>109</v>
       </c>
       <c r="C22" s="11">
         <v>7.6466430000000001</v>
@@ -5032,20 +5919,20 @@
       <c r="D22" s="11">
         <v>7.6466430000000001</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="33">
         <v>7.6466430000000001</v>
       </c>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="44" t="s">
-        <v>121</v>
+      <c r="B23" s="43" t="s">
+        <v>114</v>
       </c>
       <c r="C23" s="11">
         <v>28.562106</v>
@@ -5053,20 +5940,20 @@
       <c r="D23" s="11">
         <v>28.562106</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="33">
         <v>28.562106</v>
       </c>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="44" t="s">
-        <v>122</v>
+      <c r="B24" s="43" t="s">
+        <v>115</v>
       </c>
       <c r="C24" s="5">
         <f>IFERROR(
@@ -5132,190 +6019,190 @@
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="E27" s="55" t="s">
-        <v>125</v>
-      </c>
-      <c r="F27" s="56"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="39" t="s">
-        <v>177</v>
+      <c r="E27" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="66"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="38" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E28" s="5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F28" s="5" cm="1">
         <f t="array" ref="F28">_xlfn._xlws.PY(1,0)</f>
         <v>9654.8938460562986</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E29" s="5" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F29" s="5" cm="1">
         <f t="array" ref="F29">_xlfn._xlws.PY(2,0)</f>
         <v>9477.3706242110438</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E30" s="5" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F30" s="5" cm="1">
         <f t="array" ref="F30">_xlfn._xlws.PY(3,0)</f>
         <v>20</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E31" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F31" s="5" cm="1">
         <f t="array" ref="F31">_xlfn._xlws.PY(4,0)</f>
         <v>14.778505604767959</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E32" s="5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F32" s="5" cm="1">
         <f t="array" ref="F32">_xlfn._xlws.PY(5,0)</f>
         <v>13321.017203557933</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="E33" s="5" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F33" s="5" cm="1">
         <f t="array" ref="F33">_xlfn._xlws.PY(6,0)</f>
         <v>18971.879786595753</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D35" s="33"/>
+      <c r="D35" s="32"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B43" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C43" s="58"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="39"/>
+      <c r="B43" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="61"/>
+      <c r="D43" s="61"/>
+      <c r="E43" s="61"/>
+      <c r="F43" s="38"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D45" s="5">
         <f>IFERROR(((9.81*6371000^2)/(INDEX($C$17:$L$17, (MATCH("LEO (ISS mission mostly)", $C$15:$L$15, 0)))))^0.5, ((9.81*6371000^2)/(6378000+400000))^0.5)</f>
         <v>7668.5932308350311</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D46" s="5">
         <f>IFERROR($D$45+((9.81*6371000^2)/(INDEX($C$17:$L$17,(MATCH("MEO",$C$15:$L$15,0)))))^0.5, $D$45+((9.81*6371000^2)/(6378000+AVERAGE(1000000, 35786000)))^0.5)</f>
         <v>11431.368573829686</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D47" s="5">
         <f>IFERROR($D$45+((9.81*6371000^2)/(INDEX($C$17:$L$17,(MATCH("GEO/GTO",$C$15:$L$15,0)))))^0.5, $D$45+((9.81*6371000^2)/42164000)^0.5)</f>
         <v>10741.65441050474</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D48" s="5">
         <f>$D$45+3200+900</f>
         <v>11768.593230835031</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="4"/>
       <c r="C49" s="5" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D49" s="5">
         <f>$D$45+4300+900</f>
         <v>12868.593230835031</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="4"/>
       <c r="C50" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D50" s="5">
         <f>$D$45 + GEOMEAN(5500, 3500) + 900</f>
@@ -5326,7 +6213,7 @@
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="7"/>
       <c r="C51" s="8" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D51" s="5">
         <f>$D$45 + GEOMEAN(6300, 7300, 8000, 8200, 8200) + 900</f>
@@ -5335,41 +6222,41 @@
       <c r="E51" s="9"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B53" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="C53" s="52"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="53"/>
-      <c r="G53" s="39"/>
+      <c r="B53" s="62" t="s">
+        <v>137</v>
+      </c>
+      <c r="C53" s="63"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="63"/>
+      <c r="F53" s="64"/>
+      <c r="G53" s="38"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B54" s="38" t="s">
-        <v>147</v>
+      <c r="B54" s="37" t="s">
+        <v>138</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C55" s="5">
         <f t="shared" ref="C55:C61" si="1">D45</f>
         <v>7668.5932308350311</v>
       </c>
-      <c r="D55" s="42">
+      <c r="D55" s="41">
         <f>IFERROR(
     ((9.81 * (6378000 ^ 2)) *
         (
@@ -5403,13 +6290,13 @@
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C56" s="5">
         <f>D46</f>
         <v>11431.368573829686</v>
       </c>
-      <c r="D56" s="42">
+      <c r="D56" s="41">
         <f>IFERROR($D$45 +
     ((9.81 * (6378000 ^ 2)) *
         (
@@ -5443,13 +6330,13 @@
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B57" s="5" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C57" s="5">
         <f t="shared" si="1"/>
         <v>10741.65441050474</v>
       </c>
-      <c r="D57" s="42">
+      <c r="D57" s="41">
         <f>IFERROR($D$45 +
     ((9.81 * (6378000 ^ 2)) *
         (
@@ -5483,79 +6370,79 @@
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C58" s="5">
         <f t="shared" si="1"/>
         <v>11768.593230835031</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C59" s="5">
         <f t="shared" si="1"/>
         <v>12868.593230835031</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C60" s="5">
         <f t="shared" si="1"/>
         <v>12956.075424531093</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B61" s="7" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C61" s="8">
         <f t="shared" si="1"/>
         <v>16131.281864605833</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B63" s="39" t="s">
-        <v>179</v>
+      <c r="B63" s="38" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -5594,57 +6481,50 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BF2A92-EDB0-493F-BE9F-61B52BCD98C8}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" customWidth="1"/>
-    <col min="10" max="10" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" customWidth="1"/>
+    <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="14" width="18.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="54"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="59"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="59"/>
+      <c r="B2" s="59"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C5" s="11">
         <v>0.9</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C6" s="11">
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -5664,31 +6544,35 @@
         <v>15</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="N9" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="P9" t="e" cm="1" vm="2">
+        <f t="array" ref="P9">_xlfn._xlws.PY(7,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>1</v>
       </c>
@@ -5696,23 +6580,23 @@
         <f>'Data Input'!$F$28</f>
         <v>9654.8938460562986</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
       <c r="G10" s="5">
         <f>B10</f>
         <v>9654.8938460562986</v>
       </c>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>1</v>
       </c>
@@ -5721,7 +6605,7 @@
         <v>9654.8938460562986</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>7</v>
@@ -5765,7 +6649,7 @@
         <v>4776.7327377850916</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>2</v>
       </c>
@@ -5774,7 +6658,7 @@
         <v>96548.938460563018</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>7</v>
@@ -5818,7 +6702,7 @@
         <v>9553.4654755701831</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>3</v>
       </c>
@@ -5827,13 +6711,13 @@
         <v>965489.38460563053</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" s="5">
         <f>IF(LeInitialSizingTable[[#This Row],[Fuel type?]] = "Solid", INDEX(IF(LeInitialSizingTable[[#This Row],[In vacuum?]] = "YES", TheDropdownMenuTable_InitialSizing[Isp (solid, vacuum)], TheDropdownMenuTable_InitialSizing[Isp (solid, SL)]), MATCH(LeInitialSizingTable[[#This Row],[Fuel]], TheDropdownMenuTable_InitialSizing[Fuel (solid)], 0)), IF(LeInitialSizingTable[[#This Row],[Fuel type?]] = "Liquid", INDEX(IF(LeInitialSizingTable[[#This Row],[In vacuum?]] = "YES", TheDropdownMenuTable_InitialSizing[Isp (liquid, vacuum)], TheDropdownMenuTable_InitialSizing[Isp (liquid, SL)]), MATCH(LeInitialSizingTable[[#This Row],[Fuel]], TheDropdownMenuTable_InitialSizing[Fuel (liquid)], 0)), INDEX(IF(LeInitialSizingTable[[#This Row],[In vacuum?]] = "YES", TheDropdownMenuTable_InitialSizing[Isp (IDFK, vacuum)], TheDropdownMenuTable_InitialSizing[Isp (IDFK, SL)]), MATCH(LeInitialSizingTable[[#This Row],[Fuel]], TheDropdownMenuTable_InitialSizing[Fuel (IDFK)], 0))))</f>
@@ -5871,7 +6755,7 @@
         <v>17532.765389947024</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>4</v>
       </c>
@@ -5916,7 +6800,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>5</v>
       </c>
@@ -5961,7 +6845,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>6</v>
       </c>
@@ -6187,442 +7071,640 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G23" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="I23" t="e" cm="1" vm="2">
-        <f t="array" ref="I23">_xlfn._xlws.PY(7,1,LeInitialSizingTable[#All])</f>
+      <c r="G23" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="I23" t="e" cm="1" vm="3">
+        <f t="array" ref="I23">_xlfn._xlws.PY(8,1,LeInitialSizingTable[#All])</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="F24" s="59" t="s">
-        <v>132</v>
-      </c>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
+      <c r="F24" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F25" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G25" s="5" cm="1">
-        <f t="array" ref="G25">_xlfn._xlws.PY(8,0,'Data Input'!$C$7)</f>
+        <f t="array" ref="G25">_xlfn._xlws.PY(9,0,'Data Input'!$C$7)</f>
         <v>3</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F26" s="5" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="G26" s="5" cm="1">
-        <f t="array" ref="G26">_xlfn._xlws.PY(9,0,$G$25)</f>
+        <f t="array" ref="G26">_xlfn._xlws.PY(10,0,$G$25)</f>
         <v>17532.765389947024</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F27" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G27" s="5" cm="1">
-        <f t="array" ref="G27">_xlfn._xlws.PY(10,0,$G$25)</f>
+        <f t="array" ref="G27">_xlfn._xlws.PY(11,0,$G$25)</f>
         <v>107169.32169122499</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F28" s="5" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="G28" s="5" cm="1">
-        <f t="array" ref="G28">_xlfn._xlws.PY(11,0,$G$25)</f>
+        <f t="array" ref="G28">_xlfn._xlws.PY(12,0,$G$25)</f>
         <v>10716932.1691225</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F29" s="5" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="G29" s="5" t="str" cm="1">
-        <f t="array" ref="G29">_xlfn._xlws.PY(12,0,$G$26,'Data Input'!$F$32)</f>
+        <f t="array" ref="G29">_xlfn._xlws.PY(13,0,$G$26,'Data Input'!$F$32)</f>
         <v>Yes! OwO</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F30" s="5" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="G30" s="5" t="str" cm="1">
-        <f t="array" ref="G30">_xlfn._xlws.PY(12,0,$G$26,'Data Input'!$F$33)</f>
+        <f t="array" ref="G30">_xlfn._xlws.PY(13,0,$G$26,'Data Input'!$F$33)</f>
         <v>No... T_T</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="C31" s="41"/>
+      <c r="C31" s="40"/>
       <c r="F31" s="5" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="41"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
+      <c r="A32" s="40"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
       <c r="F32" s="5" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="G32" s="5" cm="1">
-        <f t="array" ref="G32">_xlfn._xlws.PY(13,0,$G$26,$G$31,$C$5,$C$6,'Data Input'!$F$32,'Data Input'!$F$33,'Data Input'!$C$7,'Data Input'!$C$7)</f>
+        <f t="array" ref="G32">_xlfn._xlws.PY(14,0,$G$26,$G$31,$C$5,$C$6,'Data Input'!$F$32,'Data Input'!$F$33,'Data Input'!$C$7,'Data Input'!$C$7)</f>
         <v>25280.940689105093</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F33" s="5" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="G33" s="5" t="str" cm="1">
-        <f t="array" ref="G33">_xlfn._xlws.PY(12,0,$G$32,'Data Input'!$F$32)</f>
+        <f t="array" ref="G33">_xlfn._xlws.PY(13,0,$G$32,'Data Input'!$F$32)</f>
         <v>Yes! OwO</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F34" s="5" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="G34" s="5" t="str" cm="1">
-        <f t="array" ref="G34">_xlfn._xlws.PY(12,0,$G$32,'Data Input'!$F$33)</f>
+        <f t="array" ref="G34">_xlfn._xlws.PY(13,0,$G$32,'Data Input'!$F$33)</f>
         <v>Yes! OwO</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="54" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="54"/>
+      <c r="A36" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="59"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="G40" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="I40" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="J40" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40" s="26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="F40" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="G40" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="H40" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I40" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="J40" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="K40" s="27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="B41" s="44" t="s">
+      <c r="B41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="44" t="s">
+      <c r="C41" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="44">
+      <c r="D41" s="43">
         <f>1.5*TheDropdownMenuTable_InitialSizing[[#This Row],[Isp (solid, SL)]]</f>
         <v>330.9</v>
       </c>
-      <c r="E41" s="44">
+      <c r="E41" s="43">
         <f>AVERAGE(220, 220, 220, 203, 240)</f>
         <v>220.6</v>
       </c>
-      <c r="F41" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="G41" s="44">
+      <c r="F41" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41" s="43">
         <v>454.84199999999998</v>
       </c>
-      <c r="H41" s="44">
+      <c r="H41" s="43">
         <v>388.78694999999999</v>
       </c>
-      <c r="I41" s="44" t="s">
+      <c r="I41" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="J41" s="44">
+      <c r="J41" s="43">
         <f>1.5*TheDropdownMenuTable_InitialSizing[[#This Row],[Isp (IDFK, SL)]]</f>
         <v>315</v>
       </c>
-      <c r="K41" s="47">
+      <c r="K41" s="46">
         <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A42" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="B42" s="44" t="s">
+      <c r="A42" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C42" s="44" t="s">
+      <c r="C42" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="44">
+      <c r="D42" s="43">
         <f>1.5*TheDropdownMenuTable_InitialSizing[[#This Row],[Isp (solid, SL)]]</f>
         <v>244.12199999999999</v>
       </c>
-      <c r="E42" s="44">
+      <c r="E42" s="43">
         <v>162.74799999999999</v>
       </c>
-      <c r="F42" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="G42" s="44">
+      <c r="F42" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" s="43">
         <v>368.50157999999999</v>
       </c>
-      <c r="H42" s="44">
+      <c r="H42" s="43">
         <v>309.27625</v>
       </c>
-      <c r="I42" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="J42" s="44">
+      <c r="I42" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="J42" s="43">
         <f>1.5*TheDropdownMenuTable_InitialSizing[[#This Row],[Isp (IDFK, SL)]]</f>
         <v>337.5</v>
       </c>
-      <c r="K42" s="47">
+      <c r="K42" s="46">
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" s="46"/>
-      <c r="B43" s="44" t="s">
+    <row r="43" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="45"/>
+      <c r="B43" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="D43" s="44">
-        <v>285.60000000000002</v>
-      </c>
-      <c r="E43" s="44">
-        <v>242</v>
-      </c>
-      <c r="F43" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="G43" s="44">
+      <c r="C43" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="D43" s="43">
+        <f>1.5*TheDropdownMenuTable_InitialSizing[[#This Row],[Isp (solid, SL)]]</f>
+        <v>393</v>
+      </c>
+      <c r="E43" s="43">
+        <v>262</v>
+      </c>
+      <c r="F43" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="G43" s="43">
         <v>357.79817000000003</v>
       </c>
-      <c r="H43" s="44">
+      <c r="H43" s="43">
         <v>299.79613000000001</v>
       </c>
-      <c r="I43" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="J43" s="44">
+      <c r="I43" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="J43" s="43">
         <f>1.5*TheDropdownMenuTable_InitialSizing[[#This Row],[Isp (IDFK, SL)]]</f>
         <v>576</v>
       </c>
-      <c r="K43" s="47">
+      <c r="K43" s="46">
         <v>384</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="46"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44" s="44">
+      <c r="A44" s="45"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="D44" s="43">
+        <f>1.5*TheDropdownMenuTable_InitialSizing[[#This Row],[Isp (solid, SL)]]</f>
+        <v>399</v>
+      </c>
+      <c r="E44" s="43">
+        <v>266</v>
+      </c>
+      <c r="F44" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="G44" s="43">
+        <v>341.38634000000002</v>
+      </c>
+      <c r="H44" s="43">
+        <v>288.58308</v>
+      </c>
+      <c r="I44" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="J44" s="84">
+        <v>316</v>
+      </c>
+      <c r="K44" s="85">
+        <f>(2*TheDropdownMenuTable_InitialSizing[[#This Row],[Isp (IDFK, vacuum)]])/3</f>
+        <v>210.66666666666666</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="45"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45" s="43">
         <f>1.5*TheDropdownMenuTable_InitialSizing[[#This Row],[Isp (solid, SL)]]</f>
         <v>116.25</v>
       </c>
-      <c r="E44" s="44">
+      <c r="E45" s="43">
         <v>77.5</v>
       </c>
-      <c r="F44" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="G44" s="44">
-        <v>341.38634000000002</v>
-      </c>
-      <c r="H44" s="44">
-        <v>288.58308</v>
-      </c>
-      <c r="I44" s="44"/>
-      <c r="J44" s="44"/>
-      <c r="K44" s="47"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" s="46"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="G45" s="44">
+      <c r="F45" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="G45" s="43">
         <v>333</v>
       </c>
-      <c r="H45" s="44">
+      <c r="H45" s="43">
         <v>285</v>
       </c>
-      <c r="I45" s="44"/>
-      <c r="J45" s="44"/>
-      <c r="K45" s="47"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="46"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="46"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="G46" s="44">
+      <c r="A46" s="45"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="G46" s="43">
         <v>343.42507999999998</v>
       </c>
-      <c r="H46" s="44">
+      <c r="H46" s="43">
         <v>291.74311999999998</v>
       </c>
-      <c r="I46" s="44"/>
-      <c r="J46" s="44"/>
-      <c r="K46" s="47"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="46"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A47" s="46"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="44"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44" t="s">
+      <c r="A47" s="45"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="G47" s="43">
+        <v>341.18247000000002</v>
+      </c>
+      <c r="H47" s="43">
+        <v>288.17532999999997</v>
+      </c>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="46"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="45"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="46"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="45"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="46"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="47"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="48"/>
+      <c r="E50" s="48"/>
+      <c r="F50" s="48"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="48"/>
+      <c r="I50" s="48"/>
+      <c r="J50" s="48"/>
+      <c r="K50" s="49"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B52" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="C52" s="61"/>
+      <c r="D52" s="61"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B54" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="5">
+        <v>32</v>
+      </c>
+      <c r="D54" s="6">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="5">
+        <v>17</v>
+      </c>
+      <c r="D55" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B56" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" s="5">
+        <v>3</v>
+      </c>
+      <c r="D56" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B57" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G47" s="44">
-        <v>341.18247000000002</v>
-      </c>
-      <c r="H47" s="44">
-        <v>288.17532999999997</v>
-      </c>
-      <c r="I47" s="44"/>
-      <c r="J47" s="44"/>
-      <c r="K47" s="47"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A48" s="46"/>
-      <c r="B48" s="44"/>
-      <c r="C48" s="44"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="44"/>
-      <c r="F48" s="44"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="44"/>
-      <c r="I48" s="44"/>
-      <c r="J48" s="44"/>
-      <c r="K48" s="47"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="46"/>
-      <c r="B49" s="44"/>
-      <c r="C49" s="44"/>
-      <c r="D49" s="44"/>
-      <c r="E49" s="44"/>
-      <c r="F49" s="44"/>
-      <c r="G49" s="44"/>
-      <c r="H49" s="44"/>
-      <c r="I49" s="44"/>
-      <c r="J49" s="44"/>
-      <c r="K49" s="47"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="48"/>
-      <c r="B50" s="49"/>
-      <c r="C50" s="49"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="49"/>
-      <c r="F50" s="49"/>
-      <c r="G50" s="49"/>
-      <c r="H50" s="49"/>
-      <c r="I50" s="49"/>
-      <c r="J50" s="49"/>
-      <c r="K50" s="50"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B52" t="s">
-        <v>178</v>
+      <c r="C57" s="5">
+        <v>11</v>
+      </c>
+      <c r="D57" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B58" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>2</v>
+      </c>
+      <c r="D58" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B59" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="5">
+        <v>1</v>
+      </c>
+      <c r="D59" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B60" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="5">
+        <v>1</v>
+      </c>
+      <c r="D60" s="6">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B61" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C61" s="5">
+        <v>1</v>
+      </c>
+      <c r="D61" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B62" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="5">
+        <v>1</v>
+      </c>
+      <c r="D62" s="6">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B63" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" s="5">
+        <v>2</v>
+      </c>
+      <c r="D63" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B64" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64" s="5">
+        <v>1</v>
+      </c>
+      <c r="D64" s="6">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B65" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="5">
+        <v>2</v>
+      </c>
+      <c r="D65" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B66" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" s="5">
+        <v>7</v>
+      </c>
+      <c r="D66" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B67" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" s="8">
+        <v>1</v>
+      </c>
+      <c r="D67" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B70" s="58" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B71" s="58" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="F24:H24"/>
+    <mergeCell ref="B52:D52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6636,14 +7718,19 @@
       <formula1>$A$41:$A$42</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="NOT AGAIN" error="What even?! Please insert valid data!" promptTitle="Fuel type 2: Electric Boogaloo" prompt="Please specify fuel type" sqref="E11:E20" xr:uid="{D3232489-5E3A-4360-884B-9C39225CAB94}">
-      <formula1>IF($D11 = "Solid", $C$41:$C$50, IF($D11 = "Liquid", $F$41:$F$50, $I$41:$I$50))</formula1>
+      <formula1>IFERROR(_xlfn.SWITCH($D11, "Solid", $C$41:$C$50, "Liquid", $F$41:$F$50, "Some weird third thing", $I$41:$I$50), "")</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="B70" r:id="rId1" xr:uid="{7ED0F5ED-0D64-479A-8B89-736242CAF90E}"/>
+    <hyperlink ref="B71" r:id="rId2" xr:uid="{DDADE4BF-8B5A-4E7C-A741-0643BCFB0DDB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-  <tableParts count="2">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
+  <legacyDrawing r:id="rId3"/>
+  <tableParts count="3">
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -6754,6 +7841,1080 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{272FC17A-FD1A-4B0E-B7EA-25C941E6F1E8}">
+  <dimension ref="B2:O82"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="59"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="83" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="73" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="74"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="77" t="s">
+        <v>225</v>
+      </c>
+      <c r="C7" s="80">
+        <f>'Data Input'!$C$7</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="73" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" s="75"/>
+      <c r="D9" s="74"/>
+      <c r="F9" s="73" t="s">
+        <v>234</v>
+      </c>
+      <c r="G9" s="74"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="93" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="78" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="94" t="s">
+        <v>241</v>
+      </c>
+      <c r="F10" s="78" t="s">
+        <v>239</v>
+      </c>
+      <c r="G10" s="78" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="77" t="s">
+        <v>277</v>
+      </c>
+      <c r="C11" s="92"/>
+      <c r="D11" s="88">
+        <f>SUM($D$12:$D$22)</f>
+        <v>25</v>
+      </c>
+      <c r="F11" s="77" t="s">
+        <v>235</v>
+      </c>
+      <c r="G11" s="79"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="77" t="s">
+        <v>278</v>
+      </c>
+      <c r="C12" s="77" t="s">
+        <v>279</v>
+      </c>
+      <c r="D12" s="79">
+        <v>4</v>
+      </c>
+      <c r="F12" s="77" t="s">
+        <v>236</v>
+      </c>
+      <c r="G12" s="79"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="79">
+        <v>5</v>
+      </c>
+      <c r="F13" s="77" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="79"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="82"/>
+      <c r="C14" s="5">
+        <v>2</v>
+      </c>
+      <c r="D14" s="79">
+        <v>6</v>
+      </c>
+      <c r="F14" s="77" t="s">
+        <v>237</v>
+      </c>
+      <c r="G14" s="79"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="82"/>
+      <c r="C15" s="5">
+        <v>3</v>
+      </c>
+      <c r="D15" s="79">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="82"/>
+      <c r="C16" s="5">
+        <v>4</v>
+      </c>
+      <c r="D16" s="79"/>
+      <c r="F16" s="91" t="s">
+        <v>242</v>
+      </c>
+      <c r="G16" s="91"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="82"/>
+      <c r="C17" s="5">
+        <v>5</v>
+      </c>
+      <c r="D17" s="79"/>
+      <c r="F17" s="76" t="s">
+        <v>243</v>
+      </c>
+      <c r="G17" s="81" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="82"/>
+      <c r="C18" s="5">
+        <v>6</v>
+      </c>
+      <c r="D18" s="79"/>
+      <c r="F18" s="76" t="s">
+        <v>244</v>
+      </c>
+      <c r="G18" s="81">
+        <f>_xlfn.IFNA(VLOOKUP($G$17, $B$71:$D$80, 2), "")</f>
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="82"/>
+      <c r="C19" s="5">
+        <v>7</v>
+      </c>
+      <c r="D19" s="79"/>
+      <c r="F19" s="76" t="s">
+        <v>245</v>
+      </c>
+      <c r="G19" s="81">
+        <f>_xlfn.IFNA(VLOOKUP($G$17, $B$71:$D$80, 3), "")</f>
+        <v>841</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="82"/>
+      <c r="C20" s="5">
+        <v>8</v>
+      </c>
+      <c r="D20" s="79"/>
+      <c r="F20" s="76" t="s">
+        <v>265</v>
+      </c>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="82"/>
+      <c r="C21" s="5">
+        <v>9</v>
+      </c>
+      <c r="D21" s="79"/>
+      <c r="F21" s="76" t="s">
+        <v>274</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="82"/>
+      <c r="C22" s="5">
+        <v>10</v>
+      </c>
+      <c r="D22" s="79"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="95" t="s">
+        <v>227</v>
+      </c>
+      <c r="C23" s="95">
+        <v>1</v>
+      </c>
+      <c r="D23" s="96"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="77"/>
+      <c r="C24" s="77">
+        <v>2</v>
+      </c>
+      <c r="D24" s="79"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="77"/>
+      <c r="C25" s="77">
+        <v>3</v>
+      </c>
+      <c r="D25" s="79"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="77"/>
+      <c r="C26" s="77">
+        <v>4</v>
+      </c>
+      <c r="D26" s="79"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="77"/>
+      <c r="C27" s="77">
+        <v>5</v>
+      </c>
+      <c r="D27" s="79"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="77"/>
+      <c r="C28" s="77">
+        <v>6</v>
+      </c>
+      <c r="D28" s="79"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="77"/>
+      <c r="C29" s="77">
+        <v>7</v>
+      </c>
+      <c r="D29" s="79"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="77"/>
+      <c r="C30" s="77">
+        <v>8</v>
+      </c>
+      <c r="D30" s="79"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="77"/>
+      <c r="C31" s="77">
+        <v>9</v>
+      </c>
+      <c r="D31" s="79"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="77"/>
+      <c r="C32" s="77">
+        <v>10</v>
+      </c>
+      <c r="D32" s="79"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="77" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="77">
+        <v>1</v>
+      </c>
+      <c r="D33" s="80" t="str">
+        <f>IF(VLOOKUP($C33, 'Initial Sizing'!$A$11:$N$20, 4, TRUE) = 0, "", VLOOKUP($C33, 'Initial Sizing'!$A$11:$N$20, 4, TRUE))</f>
+        <v>Solid</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B34" s="77"/>
+      <c r="C34" s="77">
+        <v>2</v>
+      </c>
+      <c r="D34" s="80" t="str">
+        <f>IF(VLOOKUP($C34, 'Initial Sizing'!$A$11:$N$20, 4, TRUE) = 0, "", VLOOKUP($C34, 'Initial Sizing'!$A$11:$N$20, 4, TRUE))</f>
+        <v>Solid</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B35" s="77"/>
+      <c r="C35" s="77">
+        <v>3</v>
+      </c>
+      <c r="D35" s="80" t="str">
+        <f>IF(VLOOKUP($C35, 'Initial Sizing'!$A$11:$N$20, 4, TRUE) = 0, "", VLOOKUP($C35, 'Initial Sizing'!$A$11:$N$20, 4, TRUE))</f>
+        <v>Liquid</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B36" s="77"/>
+      <c r="C36" s="77">
+        <v>4</v>
+      </c>
+      <c r="D36" s="80" t="str">
+        <f>IF(VLOOKUP($C36, 'Initial Sizing'!$A$11:$N$20, 4, TRUE) = 0, "", VLOOKUP($C36, 'Initial Sizing'!$A$11:$N$20, 4, TRUE))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B37" s="77"/>
+      <c r="C37" s="77">
+        <v>5</v>
+      </c>
+      <c r="D37" s="80" t="str">
+        <f>IF(VLOOKUP($C37, 'Initial Sizing'!$A$11:$N$20, 4, TRUE) = 0, "", VLOOKUP($C37, 'Initial Sizing'!$A$11:$N$20, 4, TRUE))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B38" s="77"/>
+      <c r="C38" s="77">
+        <v>6</v>
+      </c>
+      <c r="D38" s="80" t="str">
+        <f>IF(VLOOKUP($C38, 'Initial Sizing'!$A$11:$N$20, 4, TRUE) = 0, "", VLOOKUP($C38, 'Initial Sizing'!$A$11:$N$20, 4, TRUE))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B39" s="77"/>
+      <c r="C39" s="77">
+        <v>7</v>
+      </c>
+      <c r="D39" s="80" t="str">
+        <f>IF(VLOOKUP($C39, 'Initial Sizing'!$A$11:$N$20, 4, TRUE) = 0, "", VLOOKUP($C39, 'Initial Sizing'!$A$11:$N$20, 4, TRUE))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B40" s="77"/>
+      <c r="C40" s="77">
+        <v>8</v>
+      </c>
+      <c r="D40" s="80" t="str">
+        <f>IF(VLOOKUP($C40, 'Initial Sizing'!$A$11:$N$20, 4, TRUE) = 0, "", VLOOKUP($C40, 'Initial Sizing'!$A$11:$N$20, 4, TRUE))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B41" s="77"/>
+      <c r="C41" s="77">
+        <v>9</v>
+      </c>
+      <c r="D41" s="80" t="str">
+        <f>IF(VLOOKUP($C41, 'Initial Sizing'!$A$11:$N$20, 4, TRUE) = 0, "", VLOOKUP($C41, 'Initial Sizing'!$A$11:$N$20, 4, TRUE))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B42" s="77"/>
+      <c r="C42" s="77">
+        <v>10</v>
+      </c>
+      <c r="D42" s="80" t="str">
+        <f>IF(VLOOKUP($C42, 'Initial Sizing'!$A$11:$N$20, 4, TRUE) = 0, "", VLOOKUP($C42, 'Initial Sizing'!$A$11:$N$20, 4, TRUE))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B43" s="77" t="s">
+        <v>233</v>
+      </c>
+      <c r="C43" s="77">
+        <v>1</v>
+      </c>
+      <c r="D43" s="79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B44" s="77"/>
+      <c r="C44" s="77">
+        <v>2</v>
+      </c>
+      <c r="D44" s="79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B45" s="77"/>
+      <c r="C45" s="77">
+        <v>3</v>
+      </c>
+      <c r="D45" s="79">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B46" s="77"/>
+      <c r="C46" s="77">
+        <v>4</v>
+      </c>
+      <c r="D46" s="79"/>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B47" s="77"/>
+      <c r="C47" s="77">
+        <v>5</v>
+      </c>
+      <c r="D47" s="79"/>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B48" s="77"/>
+      <c r="C48" s="77">
+        <v>6</v>
+      </c>
+      <c r="D48" s="79"/>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B49" s="77"/>
+      <c r="C49" s="77">
+        <v>7</v>
+      </c>
+      <c r="D49" s="79"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B50" s="77"/>
+      <c r="C50" s="77">
+        <v>8</v>
+      </c>
+      <c r="D50" s="79"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B51" s="77"/>
+      <c r="C51" s="77">
+        <v>9</v>
+      </c>
+      <c r="D51" s="79"/>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B52" s="77"/>
+      <c r="C52" s="77">
+        <v>10</v>
+      </c>
+      <c r="D52" s="79"/>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B53" s="77" t="s">
+        <v>228</v>
+      </c>
+      <c r="C53" s="77">
+        <v>1</v>
+      </c>
+      <c r="D53" s="79" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B54" s="77"/>
+      <c r="C54" s="77">
+        <v>2</v>
+      </c>
+      <c r="D54" s="79" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B55" s="77"/>
+      <c r="C55" s="77">
+        <v>3</v>
+      </c>
+      <c r="D55" s="79" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B56" s="77"/>
+      <c r="C56" s="77">
+        <v>4</v>
+      </c>
+      <c r="D56" s="79"/>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B57" s="77"/>
+      <c r="C57" s="77">
+        <v>5</v>
+      </c>
+      <c r="D57" s="79"/>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B58" s="77"/>
+      <c r="C58" s="77">
+        <v>6</v>
+      </c>
+      <c r="D58" s="79"/>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B59" s="77"/>
+      <c r="C59" s="77">
+        <v>7</v>
+      </c>
+      <c r="D59" s="79"/>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B60" s="77"/>
+      <c r="C60" s="77">
+        <v>8</v>
+      </c>
+      <c r="D60" s="79"/>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B61" s="77"/>
+      <c r="C61" s="77">
+        <v>9</v>
+      </c>
+      <c r="D61" s="79"/>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B62" s="77"/>
+      <c r="C62" s="77">
+        <v>10</v>
+      </c>
+      <c r="D62" s="79"/>
+      <c r="E62" s="86"/>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="E63" s="34"/>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="E64" s="87"/>
+      <c r="F64" s="87"/>
+      <c r="G64" s="87"/>
+      <c r="H64" s="87"/>
+      <c r="I64" s="87"/>
+      <c r="J64" s="87"/>
+      <c r="K64" s="72"/>
+      <c r="L64" s="72"/>
+      <c r="M64" s="72"/>
+      <c r="N64" s="72"/>
+      <c r="O64" s="72"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B65" s="77" t="s">
+        <v>228</v>
+      </c>
+      <c r="C65" s="80" t="s">
+        <v>250</v>
+      </c>
+      <c r="E65" s="72"/>
+      <c r="F65" s="87"/>
+      <c r="G65" s="87"/>
+      <c r="H65" s="87"/>
+      <c r="I65" s="87"/>
+      <c r="J65" s="87"/>
+      <c r="K65" s="87"/>
+      <c r="L65" s="87"/>
+      <c r="M65" s="72"/>
+      <c r="N65" s="72"/>
+      <c r="O65" s="72"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B66" s="5"/>
+      <c r="C66" s="80" t="s">
+        <v>249</v>
+      </c>
+      <c r="E66" s="72"/>
+      <c r="F66" s="87"/>
+      <c r="G66" s="87"/>
+      <c r="H66" s="87"/>
+      <c r="I66" s="87"/>
+      <c r="J66" s="87"/>
+      <c r="K66" s="87"/>
+      <c r="L66" s="87"/>
+      <c r="M66" s="72"/>
+      <c r="N66" s="72"/>
+      <c r="O66" s="72"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B67" s="5"/>
+      <c r="C67" s="80" t="s">
+        <v>252</v>
+      </c>
+      <c r="E67" s="72"/>
+      <c r="F67" s="87"/>
+      <c r="G67" s="87"/>
+      <c r="H67" s="87"/>
+      <c r="I67" s="87"/>
+      <c r="J67" s="87"/>
+      <c r="K67" s="87"/>
+      <c r="L67" s="87"/>
+      <c r="M67" s="72"/>
+      <c r="N67" s="72"/>
+      <c r="O67" s="72"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B68" s="5"/>
+      <c r="C68" s="80" t="s">
+        <v>253</v>
+      </c>
+      <c r="E68" s="72"/>
+      <c r="F68" s="87"/>
+      <c r="G68" s="87"/>
+      <c r="H68" s="87"/>
+      <c r="I68" s="87"/>
+      <c r="J68" s="87"/>
+      <c r="K68" s="87"/>
+      <c r="L68" s="87"/>
+      <c r="M68" s="72"/>
+      <c r="N68" s="72"/>
+      <c r="O68" s="72"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B69" s="5"/>
+      <c r="C69" s="80" t="s">
+        <v>251</v>
+      </c>
+      <c r="E69" s="72"/>
+      <c r="F69" s="87"/>
+      <c r="G69" s="87"/>
+      <c r="H69" s="87"/>
+      <c r="I69" s="87"/>
+      <c r="J69" s="87"/>
+      <c r="K69" s="87"/>
+      <c r="L69" s="87"/>
+      <c r="M69" s="72"/>
+      <c r="N69" s="72"/>
+      <c r="O69" s="72"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B70" s="8"/>
+      <c r="C70" s="88" t="s">
+        <v>248</v>
+      </c>
+      <c r="E70" s="72"/>
+      <c r="F70" s="87"/>
+      <c r="G70" s="87"/>
+      <c r="H70" s="87"/>
+      <c r="I70" s="87"/>
+      <c r="J70" s="87"/>
+      <c r="K70" s="87"/>
+      <c r="L70" s="87"/>
+      <c r="M70" s="72"/>
+      <c r="N70" s="72"/>
+      <c r="O70" s="72"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B71" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="C71" s="78" t="s">
+        <v>255</v>
+      </c>
+      <c r="D71" s="78" t="s">
+        <v>256</v>
+      </c>
+      <c r="E71" s="72"/>
+      <c r="F71" s="72"/>
+      <c r="G71" s="72"/>
+      <c r="H71" s="72"/>
+      <c r="I71" s="72"/>
+      <c r="J71" s="72"/>
+      <c r="K71" s="72"/>
+      <c r="L71" s="72"/>
+      <c r="M71" s="72"/>
+      <c r="N71" s="72"/>
+      <c r="O71" s="72"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B72" s="77" t="s">
+        <v>266</v>
+      </c>
+      <c r="C72" s="89">
+        <v>2378</v>
+      </c>
+      <c r="D72" s="89">
+        <v>1682</v>
+      </c>
+      <c r="E72" s="72"/>
+      <c r="F72" s="72"/>
+      <c r="G72" s="72"/>
+      <c r="H72" s="72"/>
+      <c r="I72" s="72"/>
+      <c r="J72" s="72"/>
+      <c r="K72" s="72"/>
+      <c r="L72" s="72"/>
+      <c r="M72" s="72"/>
+      <c r="N72" s="72"/>
+      <c r="O72" s="72"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B73" s="77" t="s">
+        <v>257</v>
+      </c>
+      <c r="C73" s="90">
+        <v>1682</v>
+      </c>
+      <c r="D73" s="90">
+        <v>1189</v>
+      </c>
+      <c r="E73" s="72"/>
+      <c r="F73" s="72"/>
+      <c r="G73" s="72"/>
+      <c r="H73" s="72"/>
+      <c r="I73" s="72"/>
+      <c r="J73" s="72"/>
+      <c r="K73" s="72"/>
+      <c r="L73" s="72"/>
+      <c r="M73" s="72"/>
+      <c r="N73" s="72"/>
+      <c r="O73" s="72"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B74" s="77" t="s">
+        <v>258</v>
+      </c>
+      <c r="C74" s="90">
+        <v>1189</v>
+      </c>
+      <c r="D74" s="90">
+        <v>841</v>
+      </c>
+      <c r="E74" s="72"/>
+      <c r="F74" s="72"/>
+      <c r="G74" s="72"/>
+      <c r="H74" s="72"/>
+      <c r="I74" s="72"/>
+      <c r="J74" s="72"/>
+      <c r="K74" s="72"/>
+      <c r="L74" s="72"/>
+      <c r="M74" s="72"/>
+      <c r="N74" s="72"/>
+      <c r="O74" s="72"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B75" s="77" t="s">
+        <v>259</v>
+      </c>
+      <c r="C75" s="90" t="s">
+        <v>267</v>
+      </c>
+      <c r="D75" s="90">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B76" s="77" t="s">
+        <v>260</v>
+      </c>
+      <c r="C76" s="90" t="s">
+        <v>268</v>
+      </c>
+      <c r="D76" s="90">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B77" s="77" t="s">
+        <v>261</v>
+      </c>
+      <c r="C77" s="90" t="s">
+        <v>269</v>
+      </c>
+      <c r="D77" s="90">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="78" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B78" s="77" t="s">
+        <v>262</v>
+      </c>
+      <c r="C78" s="90" t="s">
+        <v>270</v>
+      </c>
+      <c r="D78" s="90">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B79" s="77" t="s">
+        <v>263</v>
+      </c>
+      <c r="C79" s="90" t="s">
+        <v>271</v>
+      </c>
+      <c r="D79" s="90">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="80" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B80" s="77" t="s">
+        <v>264</v>
+      </c>
+      <c r="C80" s="90" t="s">
+        <v>272</v>
+      </c>
+      <c r="D80" s="90">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B81" s="76" t="s">
+        <v>274</v>
+      </c>
+      <c r="C81" s="90" t="s">
+        <v>275</v>
+      </c>
+      <c r="D81" s="72"/>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B82" s="5"/>
+      <c r="C82" s="90" t="s">
+        <v>276</v>
+      </c>
+      <c r="D82" s="72"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C65:C70">
+    <sortCondition ref="C65:C70"/>
+  </sortState>
+  <mergeCells count="6">
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="B4:G4"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="NOPE!" error="That option's not available! Select only from the ones provided. " promptTitle="How would you arrange them?" prompt="Select which engine configuration would you use for each stage. " sqref="D53:D62" xr:uid="{65A90F21-9893-4B25-97E3-C548A669CA53}">
+      <formula1>_xlfn.SWITCH(MOD($D43, 2), 0, IF($D43 = 1, $C$70,$C$65:$C$68), 1, $C$65:$C$69)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G17" xr:uid="{5B62DBA2-7577-45F7-AFE9-F875891B19F6}">
+      <formula1>$B$72:$B$80</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G21" xr:uid="{1F827DD0-E19B-4FCC-87E9-645D7645B67D}">
+      <formula1>$C$81:$C$82</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75C8C883-2FC4-4407-88C0-2A8836A4633C}">
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="59"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="59"/>
+      <c r="B2" s="59"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" s="68"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="50" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" t="s">
+        <v>199</v>
+      </c>
+      <c r="G5" t="s">
+        <v>200</v>
+      </c>
+      <c r="H5" t="s">
+        <v>206</v>
+      </c>
+      <c r="I5" t="s">
+        <v>200</v>
+      </c>
+      <c r="J5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="6">
+        <f>'Initial Sizing'!$C$5</f>
+        <v>0.9</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="6">
+        <f>'Initial Sizing'!$C$6</f>
+        <v>0.1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="6">
+        <f>'Initial Sizing'!$G$27</f>
+        <v>107169.32169122499</v>
+      </c>
+      <c r="E8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="6">
+        <f>'Initial Sizing'!$G$28</f>
+        <v>10716932.1691225</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B10" s="9">
+        <f>MAX('Initial Sizing'!$G$26, 'Initial Sizing'!$G$32)</f>
+        <v>25280.940689105093</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="54">
+        <v>1</v>
+      </c>
+      <c r="B13" s="56"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="54">
+        <v>2</v>
+      </c>
+      <c r="B14" s="56"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="54">
+        <v>3</v>
+      </c>
+      <c r="B15" s="56"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="54">
+        <v>4</v>
+      </c>
+      <c r="B16" s="56"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="54">
+        <v>5</v>
+      </c>
+      <c r="B17" s="56"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="54">
+        <v>6</v>
+      </c>
+      <c r="B18" s="56"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="54">
+        <v>7</v>
+      </c>
+      <c r="B19" s="56"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="54">
+        <v>8</v>
+      </c>
+      <c r="B20" s="56"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="54">
+        <v>9</v>
+      </c>
+      <c r="B21" s="56"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="55">
+        <v>10</v>
+      </c>
+      <c r="B22" s="57"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C523EF66-94E0-40B7-ABA4-DDB7F41E44FC}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A2:H155"/>
@@ -6767,1201 +8928,1241 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="54" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" s="60"/>
+      <c r="B2" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="69"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="62" t="s">
-        <v>136</v>
-      </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="A3" s="71" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="26" t="s">
+    </row>
+    <row r="6" spans="1:8" s="34" customFormat="1" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="70" t="s">
+        <v>282</v>
+      </c>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+    </row>
+    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="35" customFormat="1" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-    </row>
-    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="H7" s="31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="17"/>
+    </row>
+    <row r="16" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="17"/>
+    </row>
+    <row r="17" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="17"/>
+    </row>
+    <row r="18" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="17"/>
+    </row>
+    <row r="19" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="17"/>
+    </row>
+    <row r="20" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="17"/>
+    </row>
+    <row r="21" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="17"/>
+    </row>
+    <row r="22" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="17"/>
+    </row>
+    <row r="23" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="17"/>
+    </row>
+    <row r="24" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="F24" s="15"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="17"/>
+    </row>
+    <row r="25" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="15"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="17"/>
+    </row>
+    <row r="26" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="F26" s="15"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="17"/>
+    </row>
+    <row r="27" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="15"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="17"/>
+    </row>
+    <row r="28" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="17"/>
+    </row>
+    <row r="29" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="20"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="20"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="15"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="15"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="G31" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
-    </row>
-    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="18"/>
-    </row>
-    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="18"/>
-    </row>
-    <row r="19" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="18"/>
-    </row>
-    <row r="20" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="18"/>
-    </row>
-    <row r="21" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="18"/>
-    </row>
-    <row r="22" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="18"/>
-    </row>
-    <row r="23" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="D23" s="18"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="16"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="18"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="16"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="18"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="18"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="16"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="18"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="16"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="18"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="16"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="18"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="18"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="21"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="21"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="16"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="16"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="G31" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H31" s="22" t="str" cm="1">
+      <c r="H31" s="21" t="str" cm="1">
         <f t="array" ref="H31">_xlfn.CONCAT(_xlfn.XLOOKUP(_xlfn.XLOOKUP(TRUE, LogTable[Who?*] &lt;&gt; "", LogTable[Who?*], "¯\_(ツ)_/¯", 0, -1), AuthorTable[Abbr.], AuthorTable[Name], "¯\_(ツ)_/¯", 0, 1), ", ", _xlfn.XLOOKUP(TRUE, LogTable[Date and Time] &lt;&gt; "", LogTable[Date and Time], "¯\_(ツ)_/¯", 0, -1))</f>
-        <v>Muhammad Naufal Afif, S.T., 21/08/2025, 21:42 UTC+7</v>
+        <v>Muhammad Naufal Afif, S.T., 23/09/2026, 22:53 UTC+7</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="16"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="18"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="17"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="16"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="16"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="18"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="16"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="18"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="17"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="16"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="17"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="16"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="18"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="17"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="16"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="18"/>
+      <c r="A38" s="15"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="16"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="18"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="17"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="16"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="18"/>
+      <c r="A40" s="15"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="17"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="16"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="18"/>
+      <c r="A41" s="15"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="17"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="16"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="18"/>
+      <c r="A42" s="15"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="16"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="18"/>
+      <c r="A43" s="15"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="17"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="16"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="18"/>
+      <c r="A44" s="15"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="17"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="16"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="18"/>
+      <c r="A45" s="15"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="17"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="16"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="18"/>
+      <c r="A46" s="15"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="16"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="18"/>
+      <c r="A47" s="15"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="17"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="16"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="18"/>
+      <c r="A48" s="15"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="17"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="16"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="18"/>
+      <c r="A49" s="15"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="17"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="16"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="18"/>
+      <c r="A50" s="15"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="16"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="18"/>
+      <c r="A51" s="15"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="17"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="16"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="18"/>
+      <c r="A52" s="15"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="17"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="16"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="18"/>
+      <c r="A53" s="15"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="17"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="16"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="18"/>
+      <c r="A54" s="15"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="16"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="18"/>
+      <c r="A55" s="15"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="17"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="16"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="18"/>
+      <c r="A56" s="15"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="17"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="16"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="18"/>
+      <c r="A57" s="15"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="17"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="16"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="18"/>
+      <c r="A58" s="15"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="16"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="18"/>
+      <c r="A59" s="15"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="17"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="16"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="18"/>
+      <c r="A60" s="15"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="17"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="16"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17"/>
-      <c r="D61" s="18"/>
+      <c r="A61" s="15"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="17"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="16"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="18"/>
+      <c r="A62" s="15"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="16"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="18"/>
+      <c r="A63" s="15"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="17"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="16"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="18"/>
+      <c r="A64" s="15"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="17"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="16"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="18"/>
+      <c r="A65" s="15"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="17"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="16"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="17"/>
-      <c r="D66" s="18"/>
+      <c r="A66" s="15"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="16"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="18"/>
+      <c r="A67" s="15"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="17"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="16"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="18"/>
+      <c r="A68" s="15"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="17"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="16"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="18"/>
+      <c r="A69" s="15"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="17"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="16"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
-      <c r="D70" s="18"/>
+      <c r="A70" s="15"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="16"/>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="18"/>
+      <c r="A71" s="15"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="17"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="16"/>
-      <c r="B72" s="17"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="18"/>
+      <c r="A72" s="15"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="17"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="16"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="17"/>
-      <c r="D73" s="18"/>
+      <c r="A73" s="15"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="17"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="16"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="17"/>
-      <c r="D74" s="18"/>
+      <c r="A74" s="15"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="16"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="18"/>
+      <c r="A75" s="15"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="17"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="16"/>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="18"/>
+      <c r="A76" s="15"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="17"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="16"/>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="18"/>
+      <c r="A77" s="15"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="17"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="16"/>
-      <c r="B78" s="17"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="18"/>
+      <c r="A78" s="15"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="16"/>
-      <c r="B79" s="17"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="18"/>
+      <c r="A79" s="15"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="17"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="16"/>
-      <c r="B80" s="17"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="18"/>
+      <c r="A80" s="15"/>
+      <c r="B80" s="16"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="17"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="16"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="18"/>
+      <c r="A81" s="15"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="17"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="16"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
-      <c r="D82" s="18"/>
+      <c r="A82" s="15"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="16"/>
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="18"/>
+      <c r="A83" s="15"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="17"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="16"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="18"/>
+      <c r="A84" s="15"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="17"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="16"/>
-      <c r="B85" s="17"/>
-      <c r="C85" s="17"/>
-      <c r="D85" s="18"/>
+      <c r="A85" s="15"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="17"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="16"/>
-      <c r="B86" s="17"/>
-      <c r="C86" s="17"/>
-      <c r="D86" s="18"/>
+      <c r="A86" s="15"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="16"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="18"/>
+      <c r="A87" s="15"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="17"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="16"/>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17"/>
-      <c r="D88" s="18"/>
+      <c r="A88" s="15"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="17"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="16"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="18"/>
+      <c r="A89" s="15"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="17"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="16"/>
-      <c r="B90" s="17"/>
-      <c r="C90" s="17"/>
-      <c r="D90" s="18"/>
+      <c r="A90" s="15"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="16"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="17"/>
-      <c r="D91" s="18"/>
+      <c r="A91" s="15"/>
+      <c r="B91" s="16"/>
+      <c r="C91" s="16"/>
+      <c r="D91" s="17"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="16"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="17"/>
-      <c r="D92" s="18"/>
+      <c r="A92" s="15"/>
+      <c r="B92" s="16"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="17"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="16"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="17"/>
-      <c r="D93" s="18"/>
+      <c r="A93" s="15"/>
+      <c r="B93" s="16"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="17"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="16"/>
-      <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
-      <c r="D94" s="18"/>
+      <c r="A94" s="15"/>
+      <c r="B94" s="16"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="16"/>
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
-      <c r="D95" s="18"/>
+      <c r="A95" s="15"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="17"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="16"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="17"/>
-      <c r="D96" s="18"/>
+      <c r="A96" s="15"/>
+      <c r="B96" s="16"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="17"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="16"/>
-      <c r="B97" s="17"/>
-      <c r="C97" s="17"/>
-      <c r="D97" s="18"/>
+      <c r="A97" s="15"/>
+      <c r="B97" s="16"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="17"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="16"/>
-      <c r="B98" s="17"/>
-      <c r="C98" s="17"/>
-      <c r="D98" s="18"/>
+      <c r="A98" s="15"/>
+      <c r="B98" s="16"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="16"/>
-      <c r="B99" s="17"/>
-      <c r="C99" s="17"/>
-      <c r="D99" s="18"/>
+      <c r="A99" s="15"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="17"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="16"/>
-      <c r="B100" s="17"/>
-      <c r="C100" s="17"/>
-      <c r="D100" s="18"/>
+      <c r="A100" s="15"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="17"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="16"/>
-      <c r="B101" s="17"/>
-      <c r="C101" s="17"/>
-      <c r="D101" s="18"/>
+      <c r="A101" s="15"/>
+      <c r="B101" s="16"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="17"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="16"/>
-      <c r="B102" s="17"/>
-      <c r="C102" s="17"/>
-      <c r="D102" s="18"/>
+      <c r="A102" s="15"/>
+      <c r="B102" s="16"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="16"/>
-      <c r="B103" s="17"/>
-      <c r="C103" s="17"/>
-      <c r="D103" s="18"/>
+      <c r="A103" s="15"/>
+      <c r="B103" s="16"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="17"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="16"/>
-      <c r="B104" s="17"/>
-      <c r="C104" s="17"/>
-      <c r="D104" s="18"/>
+      <c r="A104" s="15"/>
+      <c r="B104" s="16"/>
+      <c r="C104" s="16"/>
+      <c r="D104" s="17"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="16"/>
-      <c r="B105" s="17"/>
-      <c r="C105" s="17"/>
-      <c r="D105" s="18"/>
+      <c r="A105" s="15"/>
+      <c r="B105" s="16"/>
+      <c r="C105" s="16"/>
+      <c r="D105" s="17"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="16"/>
-      <c r="B106" s="17"/>
-      <c r="C106" s="17"/>
-      <c r="D106" s="18"/>
+      <c r="A106" s="15"/>
+      <c r="B106" s="16"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="17"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="16"/>
-      <c r="B107" s="17"/>
-      <c r="C107" s="17"/>
-      <c r="D107" s="18"/>
+      <c r="A107" s="15"/>
+      <c r="B107" s="16"/>
+      <c r="C107" s="16"/>
+      <c r="D107" s="17"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="16"/>
-      <c r="B108" s="17"/>
-      <c r="C108" s="17"/>
-      <c r="D108" s="18"/>
+      <c r="A108" s="15"/>
+      <c r="B108" s="16"/>
+      <c r="C108" s="16"/>
+      <c r="D108" s="17"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="16"/>
-      <c r="B109" s="17"/>
-      <c r="C109" s="17"/>
-      <c r="D109" s="18"/>
+      <c r="A109" s="15"/>
+      <c r="B109" s="16"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="17"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="16"/>
-      <c r="B110" s="17"/>
-      <c r="C110" s="17"/>
-      <c r="D110" s="18"/>
+      <c r="A110" s="15"/>
+      <c r="B110" s="16"/>
+      <c r="C110" s="16"/>
+      <c r="D110" s="17"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="16"/>
-      <c r="B111" s="17"/>
-      <c r="C111" s="17"/>
-      <c r="D111" s="18"/>
+      <c r="A111" s="15"/>
+      <c r="B111" s="16"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="17"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="16"/>
-      <c r="B112" s="17"/>
-      <c r="C112" s="17"/>
-      <c r="D112" s="18"/>
+      <c r="A112" s="15"/>
+      <c r="B112" s="16"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="17"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="16"/>
-      <c r="B113" s="17"/>
-      <c r="C113" s="17"/>
-      <c r="D113" s="18"/>
+      <c r="A113" s="15"/>
+      <c r="B113" s="16"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="17"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="16"/>
-      <c r="B114" s="17"/>
-      <c r="C114" s="17"/>
-      <c r="D114" s="18"/>
+      <c r="A114" s="15"/>
+      <c r="B114" s="16"/>
+      <c r="C114" s="16"/>
+      <c r="D114" s="17"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="16"/>
-      <c r="B115" s="17"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="18"/>
+      <c r="A115" s="15"/>
+      <c r="B115" s="16"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="17"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="16"/>
-      <c r="B116" s="17"/>
-      <c r="C116" s="17"/>
-      <c r="D116" s="18"/>
+      <c r="A116" s="15"/>
+      <c r="B116" s="16"/>
+      <c r="C116" s="16"/>
+      <c r="D116" s="17"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="16"/>
-      <c r="B117" s="17"/>
-      <c r="C117" s="17"/>
-      <c r="D117" s="18"/>
+      <c r="A117" s="15"/>
+      <c r="B117" s="16"/>
+      <c r="C117" s="16"/>
+      <c r="D117" s="17"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="16"/>
-      <c r="B118" s="17"/>
-      <c r="C118" s="17"/>
-      <c r="D118" s="18"/>
+      <c r="A118" s="15"/>
+      <c r="B118" s="16"/>
+      <c r="C118" s="16"/>
+      <c r="D118" s="17"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="16"/>
-      <c r="B119" s="17"/>
-      <c r="C119" s="17"/>
-      <c r="D119" s="18"/>
+      <c r="A119" s="15"/>
+      <c r="B119" s="16"/>
+      <c r="C119" s="16"/>
+      <c r="D119" s="17"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="16"/>
-      <c r="B120" s="17"/>
-      <c r="C120" s="17"/>
-      <c r="D120" s="18"/>
+      <c r="A120" s="15"/>
+      <c r="B120" s="16"/>
+      <c r="C120" s="16"/>
+      <c r="D120" s="17"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="16"/>
-      <c r="B121" s="17"/>
-      <c r="C121" s="17"/>
-      <c r="D121" s="18"/>
+      <c r="A121" s="15"/>
+      <c r="B121" s="16"/>
+      <c r="C121" s="16"/>
+      <c r="D121" s="17"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="16"/>
-      <c r="B122" s="17"/>
-      <c r="C122" s="17"/>
-      <c r="D122" s="18"/>
+      <c r="A122" s="15"/>
+      <c r="B122" s="16"/>
+      <c r="C122" s="16"/>
+      <c r="D122" s="17"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="16"/>
-      <c r="B123" s="17"/>
-      <c r="C123" s="17"/>
-      <c r="D123" s="18"/>
+      <c r="A123" s="15"/>
+      <c r="B123" s="16"/>
+      <c r="C123" s="16"/>
+      <c r="D123" s="17"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="16"/>
-      <c r="B124" s="17"/>
-      <c r="C124" s="17"/>
-      <c r="D124" s="18"/>
+      <c r="A124" s="15"/>
+      <c r="B124" s="16"/>
+      <c r="C124" s="16"/>
+      <c r="D124" s="17"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="16"/>
-      <c r="B125" s="17"/>
-      <c r="C125" s="17"/>
-      <c r="D125" s="18"/>
+      <c r="A125" s="15"/>
+      <c r="B125" s="16"/>
+      <c r="C125" s="16"/>
+      <c r="D125" s="17"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="16"/>
-      <c r="B126" s="17"/>
-      <c r="C126" s="17"/>
-      <c r="D126" s="18"/>
+      <c r="A126" s="15"/>
+      <c r="B126" s="16"/>
+      <c r="C126" s="16"/>
+      <c r="D126" s="17"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="16"/>
-      <c r="B127" s="17"/>
-      <c r="C127" s="17"/>
-      <c r="D127" s="18"/>
+      <c r="A127" s="15"/>
+      <c r="B127" s="16"/>
+      <c r="C127" s="16"/>
+      <c r="D127" s="17"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="16"/>
-      <c r="B128" s="17"/>
-      <c r="C128" s="17"/>
-      <c r="D128" s="18"/>
+      <c r="A128" s="15"/>
+      <c r="B128" s="16"/>
+      <c r="C128" s="16"/>
+      <c r="D128" s="17"/>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="16"/>
-      <c r="B129" s="17"/>
-      <c r="C129" s="17"/>
-      <c r="D129" s="18"/>
+      <c r="A129" s="15"/>
+      <c r="B129" s="16"/>
+      <c r="C129" s="16"/>
+      <c r="D129" s="17"/>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="16"/>
-      <c r="B130" s="17"/>
-      <c r="C130" s="17"/>
-      <c r="D130" s="18"/>
+      <c r="A130" s="15"/>
+      <c r="B130" s="16"/>
+      <c r="C130" s="16"/>
+      <c r="D130" s="17"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="16"/>
-      <c r="B131" s="17"/>
-      <c r="C131" s="17"/>
-      <c r="D131" s="18"/>
+      <c r="A131" s="15"/>
+      <c r="B131" s="16"/>
+      <c r="C131" s="16"/>
+      <c r="D131" s="17"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="16"/>
-      <c r="B132" s="17"/>
-      <c r="C132" s="17"/>
-      <c r="D132" s="18"/>
+      <c r="A132" s="15"/>
+      <c r="B132" s="16"/>
+      <c r="C132" s="16"/>
+      <c r="D132" s="17"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="16"/>
-      <c r="B133" s="17"/>
-      <c r="C133" s="17"/>
-      <c r="D133" s="18"/>
+      <c r="A133" s="15"/>
+      <c r="B133" s="16"/>
+      <c r="C133" s="16"/>
+      <c r="D133" s="17"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="16"/>
-      <c r="B134" s="17"/>
-      <c r="C134" s="17"/>
-      <c r="D134" s="18"/>
+      <c r="A134" s="15"/>
+      <c r="B134" s="16"/>
+      <c r="C134" s="16"/>
+      <c r="D134" s="17"/>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="16"/>
-      <c r="B135" s="17"/>
-      <c r="C135" s="17"/>
-      <c r="D135" s="18"/>
+      <c r="A135" s="15"/>
+      <c r="B135" s="16"/>
+      <c r="C135" s="16"/>
+      <c r="D135" s="17"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="16"/>
-      <c r="B136" s="17"/>
-      <c r="C136" s="17"/>
-      <c r="D136" s="18"/>
+      <c r="A136" s="15"/>
+      <c r="B136" s="16"/>
+      <c r="C136" s="16"/>
+      <c r="D136" s="17"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="16"/>
-      <c r="B137" s="17"/>
-      <c r="C137" s="17"/>
-      <c r="D137" s="18"/>
+      <c r="A137" s="15"/>
+      <c r="B137" s="16"/>
+      <c r="C137" s="16"/>
+      <c r="D137" s="17"/>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="16"/>
-      <c r="B138" s="17"/>
-      <c r="C138" s="17"/>
-      <c r="D138" s="18"/>
+      <c r="A138" s="15"/>
+      <c r="B138" s="16"/>
+      <c r="C138" s="16"/>
+      <c r="D138" s="17"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="16"/>
-      <c r="B139" s="17"/>
-      <c r="C139" s="17"/>
-      <c r="D139" s="18"/>
+      <c r="A139" s="15"/>
+      <c r="B139" s="16"/>
+      <c r="C139" s="16"/>
+      <c r="D139" s="17"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="16"/>
-      <c r="B140" s="17"/>
-      <c r="C140" s="17"/>
-      <c r="D140" s="18"/>
+      <c r="A140" s="15"/>
+      <c r="B140" s="16"/>
+      <c r="C140" s="16"/>
+      <c r="D140" s="17"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="16"/>
-      <c r="B141" s="17"/>
-      <c r="C141" s="17"/>
-      <c r="D141" s="18"/>
+      <c r="A141" s="15"/>
+      <c r="B141" s="16"/>
+      <c r="C141" s="16"/>
+      <c r="D141" s="17"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="16"/>
-      <c r="B142" s="17"/>
-      <c r="C142" s="17"/>
-      <c r="D142" s="18"/>
+      <c r="A142" s="15"/>
+      <c r="B142" s="16"/>
+      <c r="C142" s="16"/>
+      <c r="D142" s="17"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="16"/>
-      <c r="B143" s="17"/>
-      <c r="C143" s="17"/>
-      <c r="D143" s="18"/>
+      <c r="A143" s="15"/>
+      <c r="B143" s="16"/>
+      <c r="C143" s="16"/>
+      <c r="D143" s="17"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="16"/>
-      <c r="B144" s="17"/>
-      <c r="C144" s="17"/>
-      <c r="D144" s="18"/>
+      <c r="A144" s="15"/>
+      <c r="B144" s="16"/>
+      <c r="C144" s="16"/>
+      <c r="D144" s="17"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="16"/>
-      <c r="B145" s="17"/>
-      <c r="C145" s="17"/>
-      <c r="D145" s="18"/>
+      <c r="A145" s="15"/>
+      <c r="B145" s="16"/>
+      <c r="C145" s="16"/>
+      <c r="D145" s="17"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="16"/>
-      <c r="B146" s="17"/>
-      <c r="C146" s="17"/>
-      <c r="D146" s="18"/>
+      <c r="A146" s="15"/>
+      <c r="B146" s="16"/>
+      <c r="C146" s="16"/>
+      <c r="D146" s="17"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="16"/>
-      <c r="B147" s="17"/>
-      <c r="C147" s="17"/>
-      <c r="D147" s="18"/>
+      <c r="A147" s="15"/>
+      <c r="B147" s="16"/>
+      <c r="C147" s="16"/>
+      <c r="D147" s="17"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="16"/>
-      <c r="B148" s="17"/>
-      <c r="C148" s="17"/>
-      <c r="D148" s="18"/>
+      <c r="A148" s="15"/>
+      <c r="B148" s="16"/>
+      <c r="C148" s="16"/>
+      <c r="D148" s="17"/>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="16"/>
-      <c r="B149" s="17"/>
-      <c r="C149" s="17"/>
-      <c r="D149" s="18"/>
+      <c r="A149" s="15"/>
+      <c r="B149" s="16"/>
+      <c r="C149" s="16"/>
+      <c r="D149" s="17"/>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="16"/>
-      <c r="B150" s="17"/>
-      <c r="C150" s="17"/>
-      <c r="D150" s="18"/>
+      <c r="A150" s="15"/>
+      <c r="B150" s="16"/>
+      <c r="C150" s="16"/>
+      <c r="D150" s="17"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="16"/>
-      <c r="B151" s="17"/>
-      <c r="C151" s="17"/>
-      <c r="D151" s="18"/>
+      <c r="A151" s="15"/>
+      <c r="B151" s="16"/>
+      <c r="C151" s="16"/>
+      <c r="D151" s="17"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" s="16"/>
-      <c r="B152" s="17"/>
-      <c r="C152" s="17"/>
-      <c r="D152" s="18"/>
+      <c r="A152" s="15"/>
+      <c r="B152" s="16"/>
+      <c r="C152" s="16"/>
+      <c r="D152" s="17"/>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" s="16"/>
-      <c r="B153" s="17"/>
-      <c r="C153" s="17"/>
-      <c r="D153" s="18"/>
+      <c r="A153" s="15"/>
+      <c r="B153" s="16"/>
+      <c r="C153" s="16"/>
+      <c r="D153" s="17"/>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A154" s="16"/>
-      <c r="B154" s="17"/>
-      <c r="C154" s="17"/>
-      <c r="D154" s="18"/>
+      <c r="A154" s="15"/>
+      <c r="B154" s="16"/>
+      <c r="C154" s="16"/>
+      <c r="D154" s="17"/>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="19"/>
-      <c r="B155" s="20"/>
-      <c r="C155" s="20"/>
-      <c r="D155" s="21"/>
+      <c r="A155" s="18"/>
+      <c r="B155" s="19"/>
+      <c r="C155" s="19"/>
+      <c r="D155" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="3">
